--- a/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者履歴情報画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者履歴情報画面_V1.0.xlsx
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1629,12 +1629,74 @@
       <c r="AF4" s="10" t="n"/>
       <c r="AG4" s="11" t="n"/>
     </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件（SCR-013 一覧列追加）: レスポンスに `denshi_dokusya_shubetsu`（電子版読者種別）・`denshi_shonin_status`（電子申込承認ステータス）を追加し、一覧では 履歴番号 → 購読種別 → 電子版読者種別 → 電子申込承認ステータス → 手続種別 の順に表示する。どちらも `t_dokusya_rireki` の既存列で JOIN 追加は不要。紙版は両方 null。</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="10" t="n"/>
+      <c r="Z5" s="10" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC5" s="10" t="n"/>
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="10" t="n"/>
+      <c r="AG5" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="35">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="C5:G5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
@@ -1646,13 +1708,17 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="R2:V2"/>
@@ -1831,7 +1897,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2257,7 +2323,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3015,7 +3081,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3226,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK172"/>
+  <dimension ref="A1:AK174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3387,7 +3453,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6922,7 +6988,11 @@
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="11" t="n"/>
-      <c r="Y75" s="17" t="inlineStr"/>
+      <c r="Y75" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z75" s="10" t="n"/>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="10" t="n"/>
@@ -6931,7 +7001,7 @@
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>販売店ID※未設定(NULL)あり</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -8142,7 +8212,11 @@
       <c r="V96" s="10" t="n"/>
       <c r="W96" s="10" t="n"/>
       <c r="X96" s="11" t="n"/>
-      <c r="Y96" s="17" t="inlineStr"/>
+      <c r="Y96" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z96" s="10" t="n"/>
       <c r="AA96" s="10" t="n"/>
       <c r="AB96" s="10" t="n"/>
@@ -8151,7 +8225,7 @@
       <c r="AE96" s="11" t="n"/>
       <c r="AF96" s="19" t="inlineStr">
         <is>
-          <t>新聞単価ID（m_tanka）</t>
+          <t>新聞単価ID（m_tanka）※未設定(NULL)あり</t>
         </is>
       </c>
       <c r="AG96" s="10" t="n"/>
@@ -8456,7 +8530,7 @@
       <c r="B102" s="31" t="n">
         <v>69</v>
       </c>
-      <c r="C102" s="39" t="n"/>
+      <c r="C102" s="38" t="n"/>
       <c r="D102" s="19" t="inlineStr">
         <is>
           <t>biko</t>
@@ -8508,16 +8582,16 @@
       <c r="AJ102" s="10" t="n"/>
       <c r="AK102" s="11" t="n"/>
     </row>
-    <row r="103" ht="18" customHeight="1">
+    <row r="103" ht="72" customHeight="1">
       <c r="B103" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="n"/>
+      <c r="C103" s="38" t="n"/>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>denshi_dokusya_shubetsu</t>
+        </is>
+      </c>
       <c r="E103" s="10" t="n"/>
       <c r="F103" s="10" t="n"/>
       <c r="G103" s="10" t="n"/>
@@ -8528,7 +8602,7 @@
       <c r="L103" s="11" t="n"/>
       <c r="M103" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N103" s="10" t="n"/>
@@ -8548,7 +8622,7 @@
       <c r="X103" s="11" t="n"/>
       <c r="Y103" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z103" s="10" t="n"/>
@@ -8559,7 +8633,7 @@
       <c r="AE103" s="11" t="n"/>
       <c r="AF103" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>電子版読者種別 ※m_code.code_category='DENSHI_DOKUSYA_SHUBETSU'を参照（0:無料, 1:有料）。紙版は電子版連携が無いため null。SCR-013 一覧の 購読種別 直後に表示</t>
         </is>
       </c>
       <c r="AG103" s="10" t="n"/>
@@ -8568,14 +8642,14 @@
       <c r="AJ103" s="10" t="n"/>
       <c r="AK103" s="11" t="n"/>
     </row>
-    <row r="104" ht="18" customHeight="1">
+    <row r="104" ht="72" customHeight="1">
       <c r="B104" s="31" t="n">
         <v>71</v>
       </c>
-      <c r="C104" s="37" t="n"/>
+      <c r="C104" s="39" t="n"/>
       <c r="D104" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>denshi_shonin_status</t>
         </is>
       </c>
       <c r="E104" s="10" t="n"/>
@@ -8608,7 +8682,7 @@
       <c r="X104" s="11" t="n"/>
       <c r="Y104" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z104" s="10" t="n"/>
@@ -8619,7 +8693,7 @@
       <c r="AE104" s="11" t="n"/>
       <c r="AF104" s="19" t="inlineStr">
         <is>
-          <t>該当件数（履歴データ全体）</t>
+          <t>電子申込承認ステータス（0:未承認, 1:承認済み, 2:否認）。m_code ではなく電子版連携の状態から導出。Web申込以外（紙版等）は null。SCR-013 一覧の 電子版読者種別 直後に表示</t>
         </is>
       </c>
       <c r="AG104" s="10" t="n"/>
@@ -8632,12 +8706,12 @@
       <c r="B105" s="31" t="n">
         <v>72</v>
       </c>
-      <c r="C105" s="38" t="n"/>
-      <c r="D105" s="19" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="n"/>
       <c r="E105" s="10" t="n"/>
       <c r="F105" s="10" t="n"/>
       <c r="G105" s="10" t="n"/>
@@ -8648,7 +8722,7 @@
       <c r="L105" s="11" t="n"/>
       <c r="M105" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N105" s="10" t="n"/>
@@ -8679,7 +8753,7 @@
       <c r="AE105" s="11" t="n"/>
       <c r="AF105" s="19" t="inlineStr">
         <is>
-          <t>現在のページ</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG105" s="10" t="n"/>
@@ -8692,10 +8766,10 @@
       <c r="B106" s="31" t="n">
         <v>73</v>
       </c>
-      <c r="C106" s="38" t="n"/>
+      <c r="C106" s="37" t="n"/>
       <c r="D106" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E106" s="10" t="n"/>
@@ -8739,7 +8813,7 @@
       <c r="AE106" s="11" t="n"/>
       <c r="AF106" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>該当件数（履歴データ全体）</t>
         </is>
       </c>
       <c r="AG106" s="10" t="n"/>
@@ -8752,10 +8826,10 @@
       <c r="B107" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="C107" s="39" t="n"/>
+      <c r="C107" s="38" t="n"/>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E107" s="10" t="n"/>
@@ -8799,7 +8873,7 @@
       <c r="AE107" s="11" t="n"/>
       <c r="AF107" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>現在のページ</t>
         </is>
       </c>
       <c r="AG107" s="10" t="n"/>
@@ -8808,64 +8882,184 @@
       <c r="AJ107" s="10" t="n"/>
       <c r="AK107" s="11" t="n"/>
     </row>
-    <row r="108" ht="19.5" customHeight="1"/>
-    <row r="109" ht="19.5" customHeight="1">
-      <c r="B109" s="40" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="31" t="n">
+        <v>75</v>
+      </c>
+      <c r="C108" s="38" t="n"/>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="n"/>
+      <c r="J108" s="10" t="n"/>
+      <c r="K108" s="10" t="n"/>
+      <c r="L108" s="11" t="n"/>
+      <c r="M108" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N108" s="10" t="n"/>
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="11" t="n"/>
+      <c r="Q108" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R108" s="10" t="n"/>
+      <c r="S108" s="11" t="n"/>
+      <c r="T108" s="17" t="inlineStr"/>
+      <c r="U108" s="10" t="n"/>
+      <c r="V108" s="10" t="n"/>
+      <c r="W108" s="10" t="n"/>
+      <c r="X108" s="11" t="n"/>
+      <c r="Y108" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z108" s="10" t="n"/>
+      <c r="AA108" s="10" t="n"/>
+      <c r="AB108" s="10" t="n"/>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="19" t="inlineStr">
+        <is>
+          <t>1ページあたりの件数</t>
+        </is>
+      </c>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="10" t="n"/>
+      <c r="AK108" s="11" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="B109" s="31" t="n">
+        <v>76</v>
+      </c>
+      <c r="C109" s="39" t="n"/>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="11" t="n"/>
+      <c r="M109" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="11" t="n"/>
+      <c r="Q109" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="11" t="n"/>
+      <c r="T109" s="17" t="inlineStr"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="11" t="n"/>
+      <c r="Y109" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
+    </row>
+    <row r="110" ht="19.5" customHeight="1"/>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="B111" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="C110" s="19" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="C112" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/dokusya/1/rireki?page=1&amp;per_page=20&amp;sort_by=rireki_no&amp;sort_order=desc</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
-      <c r="L110" s="10" t="n"/>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="n"/>
-      <c r="O110" s="10" t="n"/>
-      <c r="P110" s="10" t="n"/>
-      <c r="Q110" s="10" t="n"/>
-      <c r="R110" s="10" t="n"/>
-      <c r="S110" s="10" t="n"/>
-      <c r="T110" s="10" t="n"/>
-      <c r="U110" s="10" t="n"/>
-      <c r="V110" s="10" t="n"/>
-      <c r="W110" s="10" t="n"/>
-      <c r="X110" s="10" t="n"/>
-      <c r="Y110" s="10" t="n"/>
-      <c r="Z110" s="10" t="n"/>
-      <c r="AA110" s="10" t="n"/>
-      <c r="AB110" s="10" t="n"/>
-      <c r="AC110" s="10" t="n"/>
-      <c r="AD110" s="10" t="n"/>
-      <c r="AE110" s="10" t="n"/>
-      <c r="AF110" s="10" t="n"/>
-      <c r="AG110" s="10" t="n"/>
-      <c r="AH110" s="10" t="n"/>
-      <c r="AI110" s="10" t="n"/>
-      <c r="AJ110" s="10" t="n"/>
-      <c r="AK110" s="11" t="n"/>
-    </row>
-    <row r="112" ht="19.5" customHeight="1">
-      <c r="B112" s="40" t="inlineStr">
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="10" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="10" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
+      <c r="U112" s="10" t="n"/>
+      <c r="V112" s="10" t="n"/>
+      <c r="W112" s="10" t="n"/>
+      <c r="X112" s="10" t="n"/>
+      <c r="Y112" s="10" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="10" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="B114" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="409" customHeight="1">
-      <c r="C113" s="19" t="inlineStr">
+    <row r="115" ht="409" customHeight="1">
+      <c r="C115" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -8895,6 +9089,8 @@
       "dokusyaso_bunrui": "一般,個人",
       "nogyosya_bunrui": "",
       "dokusya_shubetsu": 1,
+      "denshi_dokusya_shubetsu": null,
+      "denshi_shonin_status": null,
       "tanka_id": 1,
       "tanka_name": "新聞購読料",
       "tanka_kingaku": 3500,
@@ -8949,50 +9145,50 @@
 }</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
-    </row>
-    <row r="115" ht="19.5" customHeight="1">
-      <c r="B115" s="40" t="inlineStr">
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
+      <c r="V115" s="10" t="n"/>
+      <c r="W115" s="10" t="n"/>
+      <c r="X115" s="10" t="n"/>
+      <c r="Y115" s="10" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="B117" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="72" customHeight="1">
-      <c r="C116" s="19" t="inlineStr">
+    <row r="118" ht="72" customHeight="1">
+      <c r="C118" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "BAD_REQUEST",
@@ -9000,50 +9196,50 @@
 }</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
-      <c r="J116" s="10" t="n"/>
-      <c r="K116" s="10" t="n"/>
-      <c r="L116" s="10" t="n"/>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="n"/>
-      <c r="O116" s="10" t="n"/>
-      <c r="P116" s="10" t="n"/>
-      <c r="Q116" s="10" t="n"/>
-      <c r="R116" s="10" t="n"/>
-      <c r="S116" s="10" t="n"/>
-      <c r="T116" s="10" t="n"/>
-      <c r="U116" s="10" t="n"/>
-      <c r="V116" s="10" t="n"/>
-      <c r="W116" s="10" t="n"/>
-      <c r="X116" s="10" t="n"/>
-      <c r="Y116" s="10" t="n"/>
-      <c r="Z116" s="10" t="n"/>
-      <c r="AA116" s="10" t="n"/>
-      <c r="AB116" s="10" t="n"/>
-      <c r="AC116" s="10" t="n"/>
-      <c r="AD116" s="10" t="n"/>
-      <c r="AE116" s="10" t="n"/>
-      <c r="AF116" s="10" t="n"/>
-      <c r="AG116" s="10" t="n"/>
-      <c r="AH116" s="10" t="n"/>
-      <c r="AI116" s="10" t="n"/>
-      <c r="AJ116" s="10" t="n"/>
-      <c r="AK116" s="11" t="n"/>
-    </row>
-    <row r="118" ht="19.5" customHeight="1">
-      <c r="B118" s="40" t="inlineStr">
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="10" t="n"/>
+      <c r="J118" s="10" t="n"/>
+      <c r="K118" s="10" t="n"/>
+      <c r="L118" s="10" t="n"/>
+      <c r="M118" s="10" t="n"/>
+      <c r="N118" s="10" t="n"/>
+      <c r="O118" s="10" t="n"/>
+      <c r="P118" s="10" t="n"/>
+      <c r="Q118" s="10" t="n"/>
+      <c r="R118" s="10" t="n"/>
+      <c r="S118" s="10" t="n"/>
+      <c r="T118" s="10" t="n"/>
+      <c r="U118" s="10" t="n"/>
+      <c r="V118" s="10" t="n"/>
+      <c r="W118" s="10" t="n"/>
+      <c r="X118" s="10" t="n"/>
+      <c r="Y118" s="10" t="n"/>
+      <c r="Z118" s="10" t="n"/>
+      <c r="AA118" s="10" t="n"/>
+      <c r="AB118" s="10" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="10" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="10" t="n"/>
+      <c r="AK118" s="11" t="n"/>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="B120" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="72" customHeight="1">
-      <c r="C119" s="19" t="inlineStr">
+    <row r="121" ht="72" customHeight="1">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -9051,50 +9247,50 @@
 }</t>
         </is>
       </c>
-      <c r="D119" s="10" t="n"/>
-      <c r="E119" s="10" t="n"/>
-      <c r="F119" s="10" t="n"/>
-      <c r="G119" s="10" t="n"/>
-      <c r="H119" s="10" t="n"/>
-      <c r="I119" s="10" t="n"/>
-      <c r="J119" s="10" t="n"/>
-      <c r="K119" s="10" t="n"/>
-      <c r="L119" s="10" t="n"/>
-      <c r="M119" s="10" t="n"/>
-      <c r="N119" s="10" t="n"/>
-      <c r="O119" s="10" t="n"/>
-      <c r="P119" s="10" t="n"/>
-      <c r="Q119" s="10" t="n"/>
-      <c r="R119" s="10" t="n"/>
-      <c r="S119" s="10" t="n"/>
-      <c r="T119" s="10" t="n"/>
-      <c r="U119" s="10" t="n"/>
-      <c r="V119" s="10" t="n"/>
-      <c r="W119" s="10" t="n"/>
-      <c r="X119" s="10" t="n"/>
-      <c r="Y119" s="10" t="n"/>
-      <c r="Z119" s="10" t="n"/>
-      <c r="AA119" s="10" t="n"/>
-      <c r="AB119" s="10" t="n"/>
-      <c r="AC119" s="10" t="n"/>
-      <c r="AD119" s="10" t="n"/>
-      <c r="AE119" s="10" t="n"/>
-      <c r="AF119" s="10" t="n"/>
-      <c r="AG119" s="10" t="n"/>
-      <c r="AH119" s="10" t="n"/>
-      <c r="AI119" s="10" t="n"/>
-      <c r="AJ119" s="10" t="n"/>
-      <c r="AK119" s="11" t="n"/>
-    </row>
-    <row r="121" ht="19.5" customHeight="1">
-      <c r="B121" s="40" t="inlineStr">
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="n"/>
+      <c r="J121" s="10" t="n"/>
+      <c r="K121" s="10" t="n"/>
+      <c r="L121" s="10" t="n"/>
+      <c r="M121" s="10" t="n"/>
+      <c r="N121" s="10" t="n"/>
+      <c r="O121" s="10" t="n"/>
+      <c r="P121" s="10" t="n"/>
+      <c r="Q121" s="10" t="n"/>
+      <c r="R121" s="10" t="n"/>
+      <c r="S121" s="10" t="n"/>
+      <c r="T121" s="10" t="n"/>
+      <c r="U121" s="10" t="n"/>
+      <c r="V121" s="10" t="n"/>
+      <c r="W121" s="10" t="n"/>
+      <c r="X121" s="10" t="n"/>
+      <c r="Y121" s="10" t="n"/>
+      <c r="Z121" s="10" t="n"/>
+      <c r="AA121" s="10" t="n"/>
+      <c r="AB121" s="10" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="10" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="10" t="n"/>
+      <c r="AK121" s="11" t="n"/>
+    </row>
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="B123" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="72" customHeight="1">
-      <c r="C122" s="19" t="inlineStr">
+    <row r="124" ht="72" customHeight="1">
+      <c r="C124" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -9102,50 +9298,50 @@
 }</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n"/>
-      <c r="E122" s="10" t="n"/>
-      <c r="F122" s="10" t="n"/>
-      <c r="G122" s="10" t="n"/>
-      <c r="H122" s="10" t="n"/>
-      <c r="I122" s="10" t="n"/>
-      <c r="J122" s="10" t="n"/>
-      <c r="K122" s="10" t="n"/>
-      <c r="L122" s="10" t="n"/>
-      <c r="M122" s="10" t="n"/>
-      <c r="N122" s="10" t="n"/>
-      <c r="O122" s="10" t="n"/>
-      <c r="P122" s="10" t="n"/>
-      <c r="Q122" s="10" t="n"/>
-      <c r="R122" s="10" t="n"/>
-      <c r="S122" s="10" t="n"/>
-      <c r="T122" s="10" t="n"/>
-      <c r="U122" s="10" t="n"/>
-      <c r="V122" s="10" t="n"/>
-      <c r="W122" s="10" t="n"/>
-      <c r="X122" s="10" t="n"/>
-      <c r="Y122" s="10" t="n"/>
-      <c r="Z122" s="10" t="n"/>
-      <c r="AA122" s="10" t="n"/>
-      <c r="AB122" s="10" t="n"/>
-      <c r="AC122" s="10" t="n"/>
-      <c r="AD122" s="10" t="n"/>
-      <c r="AE122" s="10" t="n"/>
-      <c r="AF122" s="10" t="n"/>
-      <c r="AG122" s="10" t="n"/>
-      <c r="AH122" s="10" t="n"/>
-      <c r="AI122" s="10" t="n"/>
-      <c r="AJ122" s="10" t="n"/>
-      <c r="AK122" s="11" t="n"/>
-    </row>
-    <row r="124" ht="19.5" customHeight="1">
-      <c r="B124" s="40" t="inlineStr">
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="10" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="10" t="n"/>
+      <c r="K124" s="10" t="n"/>
+      <c r="L124" s="10" t="n"/>
+      <c r="M124" s="10" t="n"/>
+      <c r="N124" s="10" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="10" t="n"/>
+      <c r="Q124" s="10" t="n"/>
+      <c r="R124" s="10" t="n"/>
+      <c r="S124" s="10" t="n"/>
+      <c r="T124" s="10" t="n"/>
+      <c r="U124" s="10" t="n"/>
+      <c r="V124" s="10" t="n"/>
+      <c r="W124" s="10" t="n"/>
+      <c r="X124" s="10" t="n"/>
+      <c r="Y124" s="10" t="n"/>
+      <c r="Z124" s="10" t="n"/>
+      <c r="AA124" s="10" t="n"/>
+      <c r="AB124" s="10" t="n"/>
+      <c r="AC124" s="10" t="n"/>
+      <c r="AD124" s="10" t="n"/>
+      <c r="AE124" s="10" t="n"/>
+      <c r="AF124" s="10" t="n"/>
+      <c r="AG124" s="10" t="n"/>
+      <c r="AH124" s="10" t="n"/>
+      <c r="AI124" s="10" t="n"/>
+      <c r="AJ124" s="10" t="n"/>
+      <c r="AK124" s="11" t="n"/>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="B126" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Data Scope Violation）</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="72" customHeight="1">
-      <c r="C125" s="19" t="inlineStr">
+    <row r="127" ht="72" customHeight="1">
+      <c r="C127" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATA_SCOPE_VIOLATION",
@@ -9153,50 +9349,50 @@
 }</t>
         </is>
       </c>
-      <c r="D125" s="10" t="n"/>
-      <c r="E125" s="10" t="n"/>
-      <c r="F125" s="10" t="n"/>
-      <c r="G125" s="10" t="n"/>
-      <c r="H125" s="10" t="n"/>
-      <c r="I125" s="10" t="n"/>
-      <c r="J125" s="10" t="n"/>
-      <c r="K125" s="10" t="n"/>
-      <c r="L125" s="10" t="n"/>
-      <c r="M125" s="10" t="n"/>
-      <c r="N125" s="10" t="n"/>
-      <c r="O125" s="10" t="n"/>
-      <c r="P125" s="10" t="n"/>
-      <c r="Q125" s="10" t="n"/>
-      <c r="R125" s="10" t="n"/>
-      <c r="S125" s="10" t="n"/>
-      <c r="T125" s="10" t="n"/>
-      <c r="U125" s="10" t="n"/>
-      <c r="V125" s="10" t="n"/>
-      <c r="W125" s="10" t="n"/>
-      <c r="X125" s="10" t="n"/>
-      <c r="Y125" s="10" t="n"/>
-      <c r="Z125" s="10" t="n"/>
-      <c r="AA125" s="10" t="n"/>
-      <c r="AB125" s="10" t="n"/>
-      <c r="AC125" s="10" t="n"/>
-      <c r="AD125" s="10" t="n"/>
-      <c r="AE125" s="10" t="n"/>
-      <c r="AF125" s="10" t="n"/>
-      <c r="AG125" s="10" t="n"/>
-      <c r="AH125" s="10" t="n"/>
-      <c r="AI125" s="10" t="n"/>
-      <c r="AJ125" s="10" t="n"/>
-      <c r="AK125" s="11" t="n"/>
-    </row>
-    <row r="127" ht="19.5" customHeight="1">
-      <c r="B127" s="40" t="inlineStr">
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="10" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="10" t="n"/>
+      <c r="I127" s="10" t="n"/>
+      <c r="J127" s="10" t="n"/>
+      <c r="K127" s="10" t="n"/>
+      <c r="L127" s="10" t="n"/>
+      <c r="M127" s="10" t="n"/>
+      <c r="N127" s="10" t="n"/>
+      <c r="O127" s="10" t="n"/>
+      <c r="P127" s="10" t="n"/>
+      <c r="Q127" s="10" t="n"/>
+      <c r="R127" s="10" t="n"/>
+      <c r="S127" s="10" t="n"/>
+      <c r="T127" s="10" t="n"/>
+      <c r="U127" s="10" t="n"/>
+      <c r="V127" s="10" t="n"/>
+      <c r="W127" s="10" t="n"/>
+      <c r="X127" s="10" t="n"/>
+      <c r="Y127" s="10" t="n"/>
+      <c r="Z127" s="10" t="n"/>
+      <c r="AA127" s="10" t="n"/>
+      <c r="AB127" s="10" t="n"/>
+      <c r="AC127" s="10" t="n"/>
+      <c r="AD127" s="10" t="n"/>
+      <c r="AE127" s="10" t="n"/>
+      <c r="AF127" s="10" t="n"/>
+      <c r="AG127" s="10" t="n"/>
+      <c r="AH127" s="10" t="n"/>
+      <c r="AI127" s="10" t="n"/>
+      <c r="AJ127" s="10" t="n"/>
+      <c r="AK127" s="11" t="n"/>
+    </row>
+    <row r="129" ht="19.5" customHeight="1">
+      <c r="B129" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="72" customHeight="1">
-      <c r="C128" s="19" t="inlineStr">
+    <row r="130" ht="72" customHeight="1">
+      <c r="C130" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -9204,50 +9400,50 @@
 }</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n"/>
-      <c r="E128" s="10" t="n"/>
-      <c r="F128" s="10" t="n"/>
-      <c r="G128" s="10" t="n"/>
-      <c r="H128" s="10" t="n"/>
-      <c r="I128" s="10" t="n"/>
-      <c r="J128" s="10" t="n"/>
-      <c r="K128" s="10" t="n"/>
-      <c r="L128" s="10" t="n"/>
-      <c r="M128" s="10" t="n"/>
-      <c r="N128" s="10" t="n"/>
-      <c r="O128" s="10" t="n"/>
-      <c r="P128" s="10" t="n"/>
-      <c r="Q128" s="10" t="n"/>
-      <c r="R128" s="10" t="n"/>
-      <c r="S128" s="10" t="n"/>
-      <c r="T128" s="10" t="n"/>
-      <c r="U128" s="10" t="n"/>
-      <c r="V128" s="10" t="n"/>
-      <c r="W128" s="10" t="n"/>
-      <c r="X128" s="10" t="n"/>
-      <c r="Y128" s="10" t="n"/>
-      <c r="Z128" s="10" t="n"/>
-      <c r="AA128" s="10" t="n"/>
-      <c r="AB128" s="10" t="n"/>
-      <c r="AC128" s="10" t="n"/>
-      <c r="AD128" s="10" t="n"/>
-      <c r="AE128" s="10" t="n"/>
-      <c r="AF128" s="10" t="n"/>
-      <c r="AG128" s="10" t="n"/>
-      <c r="AH128" s="10" t="n"/>
-      <c r="AI128" s="10" t="n"/>
-      <c r="AJ128" s="10" t="n"/>
-      <c r="AK128" s="11" t="n"/>
-    </row>
-    <row r="130" ht="19.5" customHeight="1">
-      <c r="B130" s="40" t="inlineStr">
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="10" t="n"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
+      <c r="H130" s="10" t="n"/>
+      <c r="I130" s="10" t="n"/>
+      <c r="J130" s="10" t="n"/>
+      <c r="K130" s="10" t="n"/>
+      <c r="L130" s="10" t="n"/>
+      <c r="M130" s="10" t="n"/>
+      <c r="N130" s="10" t="n"/>
+      <c r="O130" s="10" t="n"/>
+      <c r="P130" s="10" t="n"/>
+      <c r="Q130" s="10" t="n"/>
+      <c r="R130" s="10" t="n"/>
+      <c r="S130" s="10" t="n"/>
+      <c r="T130" s="10" t="n"/>
+      <c r="U130" s="10" t="n"/>
+      <c r="V130" s="10" t="n"/>
+      <c r="W130" s="10" t="n"/>
+      <c r="X130" s="10" t="n"/>
+      <c r="Y130" s="10" t="n"/>
+      <c r="Z130" s="10" t="n"/>
+      <c r="AA130" s="10" t="n"/>
+      <c r="AB130" s="10" t="n"/>
+      <c r="AC130" s="10" t="n"/>
+      <c r="AD130" s="10" t="n"/>
+      <c r="AE130" s="10" t="n"/>
+      <c r="AF130" s="10" t="n"/>
+      <c r="AG130" s="10" t="n"/>
+      <c r="AH130" s="10" t="n"/>
+      <c r="AI130" s="10" t="n"/>
+      <c r="AJ130" s="10" t="n"/>
+      <c r="AK130" s="11" t="n"/>
+    </row>
+    <row r="132" ht="19.5" customHeight="1">
+      <c r="B132" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 429 Too Many Requests）</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="72" customHeight="1">
-      <c r="C131" s="19" t="inlineStr">
+    <row r="133" ht="72" customHeight="1">
+      <c r="C133" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "TOO_MANY_REQUESTS",
@@ -9255,50 +9451,50 @@
 }</t>
         </is>
       </c>
-      <c r="D131" s="10" t="n"/>
-      <c r="E131" s="10" t="n"/>
-      <c r="F131" s="10" t="n"/>
-      <c r="G131" s="10" t="n"/>
-      <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="n"/>
-      <c r="J131" s="10" t="n"/>
-      <c r="K131" s="10" t="n"/>
-      <c r="L131" s="10" t="n"/>
-      <c r="M131" s="10" t="n"/>
-      <c r="N131" s="10" t="n"/>
-      <c r="O131" s="10" t="n"/>
-      <c r="P131" s="10" t="n"/>
-      <c r="Q131" s="10" t="n"/>
-      <c r="R131" s="10" t="n"/>
-      <c r="S131" s="10" t="n"/>
-      <c r="T131" s="10" t="n"/>
-      <c r="U131" s="10" t="n"/>
-      <c r="V131" s="10" t="n"/>
-      <c r="W131" s="10" t="n"/>
-      <c r="X131" s="10" t="n"/>
-      <c r="Y131" s="10" t="n"/>
-      <c r="Z131" s="10" t="n"/>
-      <c r="AA131" s="10" t="n"/>
-      <c r="AB131" s="10" t="n"/>
-      <c r="AC131" s="10" t="n"/>
-      <c r="AD131" s="10" t="n"/>
-      <c r="AE131" s="10" t="n"/>
-      <c r="AF131" s="10" t="n"/>
-      <c r="AG131" s="10" t="n"/>
-      <c r="AH131" s="10" t="n"/>
-      <c r="AI131" s="10" t="n"/>
-      <c r="AJ131" s="10" t="n"/>
-      <c r="AK131" s="11" t="n"/>
-    </row>
-    <row r="133" ht="19.5" customHeight="1">
-      <c r="B133" s="40" t="inlineStr">
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="10" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="10" t="n"/>
+      <c r="J133" s="10" t="n"/>
+      <c r="K133" s="10" t="n"/>
+      <c r="L133" s="10" t="n"/>
+      <c r="M133" s="10" t="n"/>
+      <c r="N133" s="10" t="n"/>
+      <c r="O133" s="10" t="n"/>
+      <c r="P133" s="10" t="n"/>
+      <c r="Q133" s="10" t="n"/>
+      <c r="R133" s="10" t="n"/>
+      <c r="S133" s="10" t="n"/>
+      <c r="T133" s="10" t="n"/>
+      <c r="U133" s="10" t="n"/>
+      <c r="V133" s="10" t="n"/>
+      <c r="W133" s="10" t="n"/>
+      <c r="X133" s="10" t="n"/>
+      <c r="Y133" s="10" t="n"/>
+      <c r="Z133" s="10" t="n"/>
+      <c r="AA133" s="10" t="n"/>
+      <c r="AB133" s="10" t="n"/>
+      <c r="AC133" s="10" t="n"/>
+      <c r="AD133" s="10" t="n"/>
+      <c r="AE133" s="10" t="n"/>
+      <c r="AF133" s="10" t="n"/>
+      <c r="AG133" s="10" t="n"/>
+      <c r="AH133" s="10" t="n"/>
+      <c r="AI133" s="10" t="n"/>
+      <c r="AJ133" s="10" t="n"/>
+      <c r="AK133" s="11" t="n"/>
+    </row>
+    <row r="135" ht="19.5" customHeight="1">
+      <c r="B135" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="72" customHeight="1">
-      <c r="C134" s="19" t="inlineStr">
+    <row r="136" ht="72" customHeight="1">
+      <c r="C136" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -9306,205 +9502,205 @@
 }</t>
         </is>
       </c>
-      <c r="D134" s="10" t="n"/>
-      <c r="E134" s="10" t="n"/>
-      <c r="F134" s="10" t="n"/>
-      <c r="G134" s="10" t="n"/>
-      <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
-      <c r="J134" s="10" t="n"/>
-      <c r="K134" s="10" t="n"/>
-      <c r="L134" s="10" t="n"/>
-      <c r="M134" s="10" t="n"/>
-      <c r="N134" s="10" t="n"/>
-      <c r="O134" s="10" t="n"/>
-      <c r="P134" s="10" t="n"/>
-      <c r="Q134" s="10" t="n"/>
-      <c r="R134" s="10" t="n"/>
-      <c r="S134" s="10" t="n"/>
-      <c r="T134" s="10" t="n"/>
-      <c r="U134" s="10" t="n"/>
-      <c r="V134" s="10" t="n"/>
-      <c r="W134" s="10" t="n"/>
-      <c r="X134" s="10" t="n"/>
-      <c r="Y134" s="10" t="n"/>
-      <c r="Z134" s="10" t="n"/>
-      <c r="AA134" s="10" t="n"/>
-      <c r="AB134" s="10" t="n"/>
-      <c r="AC134" s="10" t="n"/>
-      <c r="AD134" s="10" t="n"/>
-      <c r="AE134" s="10" t="n"/>
-      <c r="AF134" s="10" t="n"/>
-      <c r="AG134" s="10" t="n"/>
-      <c r="AH134" s="10" t="n"/>
-      <c r="AI134" s="10" t="n"/>
-      <c r="AJ134" s="10" t="n"/>
-      <c r="AK134" s="11" t="n"/>
-    </row>
-    <row r="136" ht="19.5" customHeight="1"/>
-    <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="27" t="inlineStr">
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="10" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="n"/>
+      <c r="I136" s="10" t="n"/>
+      <c r="J136" s="10" t="n"/>
+      <c r="K136" s="10" t="n"/>
+      <c r="L136" s="10" t="n"/>
+      <c r="M136" s="10" t="n"/>
+      <c r="N136" s="10" t="n"/>
+      <c r="O136" s="10" t="n"/>
+      <c r="P136" s="10" t="n"/>
+      <c r="Q136" s="10" t="n"/>
+      <c r="R136" s="10" t="n"/>
+      <c r="S136" s="10" t="n"/>
+      <c r="T136" s="10" t="n"/>
+      <c r="U136" s="10" t="n"/>
+      <c r="V136" s="10" t="n"/>
+      <c r="W136" s="10" t="n"/>
+      <c r="X136" s="10" t="n"/>
+      <c r="Y136" s="10" t="n"/>
+      <c r="Z136" s="10" t="n"/>
+      <c r="AA136" s="10" t="n"/>
+      <c r="AB136" s="10" t="n"/>
+      <c r="AC136" s="10" t="n"/>
+      <c r="AD136" s="10" t="n"/>
+      <c r="AE136" s="10" t="n"/>
+      <c r="AF136" s="10" t="n"/>
+      <c r="AG136" s="10" t="n"/>
+      <c r="AH136" s="10" t="n"/>
+      <c r="AI136" s="10" t="n"/>
+      <c r="AJ136" s="10" t="n"/>
+      <c r="AK136" s="11" t="n"/>
+    </row>
+    <row r="138" ht="19.5" customHeight="1"/>
+    <row r="139" ht="19.5" customHeight="1">
+      <c r="A139" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="B138" s="27" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="B140" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="C139" s="41" t="inlineStr">
-        <is>
-          <t>パスパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="D140" s="41" t="inlineStr">
-        <is>
-          <t>`dokusya_id`：数値型、必須。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="C141" s="41" t="inlineStr">
         <is>
-          <t>クエリパラメータの検証：</t>
+          <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="D142" s="41" t="inlineStr">
         <is>
+          <t>`dokusya_id`：数値型、必須。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="C143" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="D144" s="41" t="inlineStr">
+        <is>
           <t>`page`：数値型、`&gt;= 1`。省略時 `1`。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="36" customHeight="1">
-      <c r="D143" s="41" t="inlineStr">
-        <is>
-          <t>`per_page`：数値型、`1 &lt;= per_page &lt;= 100`。省略時 `20`（機能定義 3.1 デフォルト 20、最大 100）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="54" customHeight="1">
-      <c r="D144" s="41" t="inlineStr">
-        <is>
-          <t>`sort_by`：許可リスト = `{rireki_no, dokusya_kaishi_date, joho_henko_tekiyo_date, created_at}`。省略時 `rireki_no`。許可リスト外の値はバリデーションエラー。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="36" customHeight="1">
       <c r="D145" s="41" t="inlineStr">
         <is>
+          <t>`per_page`：数値型、`1 &lt;= per_page &lt;= 100`。省略時 `20`（機能定義 3.1 デフォルト 20、最大 100）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="54" customHeight="1">
+      <c r="D146" s="41" t="inlineStr">
+        <is>
+          <t>`sort_by`：許可リスト = `{rireki_no, dokusya_kaishi_date, joho_henko_tekiyo_date, created_at}`。省略時 `rireki_no`。許可リスト外の値はバリデーションエラー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="D147" s="41" t="inlineStr">
+        <is>
           <t>`sort_order`：許可リスト = `{asc, desc}`。省略時 `desc`（機能定義 1.2 最新レコードを先頭）。</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="36" customHeight="1">
-      <c r="C146" s="41" t="inlineStr">
+    <row r="148" ht="36" customHeight="1">
+      <c r="C148" s="41" t="inlineStr">
         <is>
           <t>バリデーション失敗時：HTTP 400 (`BAD_REQUEST` / `VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="B147" s="27" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="B149" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="C148" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="C149" s="41" t="inlineStr">
-        <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="C150" s="41" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.view`</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="36" customHeight="1">
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
       <c r="C151" s="41" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN（seeder.md §3 マトリクス No.2）</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="C152" s="41" t="inlineStr">
         <is>
+          <t>必要権限: `dokusya.view`</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="36" customHeight="1">
+      <c r="C153" s="41" t="inlineStr">
+        <is>
+          <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN（seeder.md §3 マトリクス No.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="C154" s="41" t="inlineStr">
+        <is>
           <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="C153" s="41" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="C155" s="41" t="inlineStr">
         <is>
           <t>DataScope（account_concept.md ※1）:</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="36" customHeight="1">
-      <c r="D154" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI: `ja_id = user.ja_id`（自中央会のレコードのみ。管轄JAの読者は閲覧不可）</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="D155" s="41" t="inlineStr">
-        <is>
-          <t>JA_HONTEN: `ja_id = user.ja_id`（自JAのみ）</t>
         </is>
       </c>
     </row>
     <row r="156" ht="36" customHeight="1">
       <c r="D156" s="41" t="inlineStr">
         <is>
+          <t>CHUOKAI: `ja_id = user.ja_id`（自中央会のレコードのみ。管轄JAの読者は閲覧不可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="D157" s="41" t="inlineStr">
+        <is>
+          <t>JA_HONTEN: `ja_id = user.ja_id`（自JAのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="36" customHeight="1">
+      <c r="D158" s="41" t="inlineStr">
+        <is>
           <t>JA_KANRI_SHITEN: `ja_id = user.ja_id AND kanri_shiten_id = user.kanri_shiten_id`（自管理支店のみ）</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="36" customHeight="1">
-      <c r="C157" s="41" t="inlineStr">
+    <row r="159" ht="36" customHeight="1">
+      <c r="C159" s="41" t="inlineStr">
         <is>
           <t>DataScope違反（他JAまたは他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="B158" s="27" t="inlineStr">
+    <row r="160" ht="18" customHeight="1">
+      <c r="B160" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="C159" s="41" t="inlineStr">
+    <row r="161" ht="18" customHeight="1">
+      <c r="C161" s="41" t="inlineStr">
         <is>
           <t>対象購読者の存在確認（DataScope内）:</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="126" customHeight="1">
-      <c r="C160" s="42" t="inlineStr">
+    <row r="162" ht="126" customHeight="1">
+      <c r="C162" s="42" t="inlineStr">
         <is>
           <t>SELECT dokusya_id, ja_id, kanri_shiten_id
 FROM m_dokusya
@@ -9515,64 +9711,64 @@
   AND (:user_kanri_shiten_id IS NULL OR kanri_shiten_id = :user_kanri_shiten_id)</t>
         </is>
       </c>
-      <c r="D160" s="10" t="n"/>
-      <c r="E160" s="10" t="n"/>
-      <c r="F160" s="10" t="n"/>
-      <c r="G160" s="10" t="n"/>
-      <c r="H160" s="10" t="n"/>
-      <c r="I160" s="10" t="n"/>
-      <c r="J160" s="10" t="n"/>
-      <c r="K160" s="10" t="n"/>
-      <c r="L160" s="10" t="n"/>
-      <c r="M160" s="10" t="n"/>
-      <c r="N160" s="10" t="n"/>
-      <c r="O160" s="10" t="n"/>
-      <c r="P160" s="10" t="n"/>
-      <c r="Q160" s="10" t="n"/>
-      <c r="R160" s="10" t="n"/>
-      <c r="S160" s="10" t="n"/>
-      <c r="T160" s="10" t="n"/>
-      <c r="U160" s="10" t="n"/>
-      <c r="V160" s="10" t="n"/>
-      <c r="W160" s="10" t="n"/>
-      <c r="X160" s="10" t="n"/>
-      <c r="Y160" s="10" t="n"/>
-      <c r="Z160" s="10" t="n"/>
-      <c r="AA160" s="10" t="n"/>
-      <c r="AB160" s="10" t="n"/>
-      <c r="AC160" s="10" t="n"/>
-      <c r="AD160" s="10" t="n"/>
-      <c r="AE160" s="10" t="n"/>
-      <c r="AF160" s="10" t="n"/>
-      <c r="AG160" s="10" t="n"/>
-      <c r="AH160" s="10" t="n"/>
-      <c r="AI160" s="10" t="n"/>
-      <c r="AJ160" s="10" t="n"/>
-      <c r="AK160" s="11" t="n"/>
-    </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="C161" s="41" t="inlineStr">
+      <c r="D162" s="10" t="n"/>
+      <c r="E162" s="10" t="n"/>
+      <c r="F162" s="10" t="n"/>
+      <c r="G162" s="10" t="n"/>
+      <c r="H162" s="10" t="n"/>
+      <c r="I162" s="10" t="n"/>
+      <c r="J162" s="10" t="n"/>
+      <c r="K162" s="10" t="n"/>
+      <c r="L162" s="10" t="n"/>
+      <c r="M162" s="10" t="n"/>
+      <c r="N162" s="10" t="n"/>
+      <c r="O162" s="10" t="n"/>
+      <c r="P162" s="10" t="n"/>
+      <c r="Q162" s="10" t="n"/>
+      <c r="R162" s="10" t="n"/>
+      <c r="S162" s="10" t="n"/>
+      <c r="T162" s="10" t="n"/>
+      <c r="U162" s="10" t="n"/>
+      <c r="V162" s="10" t="n"/>
+      <c r="W162" s="10" t="n"/>
+      <c r="X162" s="10" t="n"/>
+      <c r="Y162" s="10" t="n"/>
+      <c r="Z162" s="10" t="n"/>
+      <c r="AA162" s="10" t="n"/>
+      <c r="AB162" s="10" t="n"/>
+      <c r="AC162" s="10" t="n"/>
+      <c r="AD162" s="10" t="n"/>
+      <c r="AE162" s="10" t="n"/>
+      <c r="AF162" s="10" t="n"/>
+      <c r="AG162" s="10" t="n"/>
+      <c r="AH162" s="10" t="n"/>
+      <c r="AI162" s="10" t="n"/>
+      <c r="AJ162" s="10" t="n"/>
+      <c r="AK162" s="11" t="n"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="C163" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="36" customHeight="1">
-      <c r="C162" s="41" t="inlineStr">
+    <row r="164" ht="36" customHeight="1">
+      <c r="C164" s="41" t="inlineStr">
         <is>
           <t>ja_id / kanri_shiten_id が DataScope と一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="B163" s="27" t="inlineStr">
+    <row r="165" ht="18" customHeight="1">
+      <c r="B165" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="108" customHeight="1">
-      <c r="C164" s="42" t="inlineStr">
+    <row r="166" ht="108" customHeight="1">
+      <c r="C166" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM t_dokusya_rireki
@@ -9582,50 +9778,50 @@
   AND (:user_kanri_shiten_id IS NULL OR kanri_shiten_id = :user_kanri_shiten_id)</t>
         </is>
       </c>
-      <c r="D164" s="10" t="n"/>
-      <c r="E164" s="10" t="n"/>
-      <c r="F164" s="10" t="n"/>
-      <c r="G164" s="10" t="n"/>
-      <c r="H164" s="10" t="n"/>
-      <c r="I164" s="10" t="n"/>
-      <c r="J164" s="10" t="n"/>
-      <c r="K164" s="10" t="n"/>
-      <c r="L164" s="10" t="n"/>
-      <c r="M164" s="10" t="n"/>
-      <c r="N164" s="10" t="n"/>
-      <c r="O164" s="10" t="n"/>
-      <c r="P164" s="10" t="n"/>
-      <c r="Q164" s="10" t="n"/>
-      <c r="R164" s="10" t="n"/>
-      <c r="S164" s="10" t="n"/>
-      <c r="T164" s="10" t="n"/>
-      <c r="U164" s="10" t="n"/>
-      <c r="V164" s="10" t="n"/>
-      <c r="W164" s="10" t="n"/>
-      <c r="X164" s="10" t="n"/>
-      <c r="Y164" s="10" t="n"/>
-      <c r="Z164" s="10" t="n"/>
-      <c r="AA164" s="10" t="n"/>
-      <c r="AB164" s="10" t="n"/>
-      <c r="AC164" s="10" t="n"/>
-      <c r="AD164" s="10" t="n"/>
-      <c r="AE164" s="10" t="n"/>
-      <c r="AF164" s="10" t="n"/>
-      <c r="AG164" s="10" t="n"/>
-      <c r="AH164" s="10" t="n"/>
-      <c r="AI164" s="10" t="n"/>
-      <c r="AJ164" s="10" t="n"/>
-      <c r="AK164" s="11" t="n"/>
-    </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="B165" s="27" t="inlineStr">
+      <c r="D166" s="10" t="n"/>
+      <c r="E166" s="10" t="n"/>
+      <c r="F166" s="10" t="n"/>
+      <c r="G166" s="10" t="n"/>
+      <c r="H166" s="10" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="10" t="n"/>
+      <c r="K166" s="10" t="n"/>
+      <c r="L166" s="10" t="n"/>
+      <c r="M166" s="10" t="n"/>
+      <c r="N166" s="10" t="n"/>
+      <c r="O166" s="10" t="n"/>
+      <c r="P166" s="10" t="n"/>
+      <c r="Q166" s="10" t="n"/>
+      <c r="R166" s="10" t="n"/>
+      <c r="S166" s="10" t="n"/>
+      <c r="T166" s="10" t="n"/>
+      <c r="U166" s="10" t="n"/>
+      <c r="V166" s="10" t="n"/>
+      <c r="W166" s="10" t="n"/>
+      <c r="X166" s="10" t="n"/>
+      <c r="Y166" s="10" t="n"/>
+      <c r="Z166" s="10" t="n"/>
+      <c r="AA166" s="10" t="n"/>
+      <c r="AB166" s="10" t="n"/>
+      <c r="AC166" s="10" t="n"/>
+      <c r="AD166" s="10" t="n"/>
+      <c r="AE166" s="10" t="n"/>
+      <c r="AF166" s="10" t="n"/>
+      <c r="AG166" s="10" t="n"/>
+      <c r="AH166" s="10" t="n"/>
+      <c r="AI166" s="10" t="n"/>
+      <c r="AJ166" s="10" t="n"/>
+      <c r="AK166" s="11" t="n"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="B167" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="409" customHeight="1">
-      <c r="C166" s="42" t="inlineStr">
+    <row r="168" ht="409" customHeight="1">
+      <c r="C168" s="42" t="inlineStr">
         <is>
           <t>SELECT
   r.dokusya_rireki_id, r.dokusya_id, r.rireki_no,
@@ -9636,7 +9832,7 @@
   r.shikuchoson, r.chome_banchi, r.tatemono_mei,
   r.renrakusaki_1, r.renrakusaki_2, r.email,
   r.mail_magazine_flg, r.birth_year, r.gender,
-  r.dokusya_shubetsu,
+  r.dokusya_shubetsu, r.denshi_dokusya_shubetsu, r.denshi_shonin_status,
   r.dokusyaso_bunrui, r.nogyosya_bunrui,
   r.tanka_id, t.tanka_name,
   /* 金額は JA の税区分で解決（zei_kubun=1 内税→税込、それ以外→税抜） */
@@ -9679,86 +9875,88 @@
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n"/>
-      <c r="E166" s="10" t="n"/>
-      <c r="F166" s="10" t="n"/>
-      <c r="G166" s="10" t="n"/>
-      <c r="H166" s="10" t="n"/>
-      <c r="I166" s="10" t="n"/>
-      <c r="J166" s="10" t="n"/>
-      <c r="K166" s="10" t="n"/>
-      <c r="L166" s="10" t="n"/>
-      <c r="M166" s="10" t="n"/>
-      <c r="N166" s="10" t="n"/>
-      <c r="O166" s="10" t="n"/>
-      <c r="P166" s="10" t="n"/>
-      <c r="Q166" s="10" t="n"/>
-      <c r="R166" s="10" t="n"/>
-      <c r="S166" s="10" t="n"/>
-      <c r="T166" s="10" t="n"/>
-      <c r="U166" s="10" t="n"/>
-      <c r="V166" s="10" t="n"/>
-      <c r="W166" s="10" t="n"/>
-      <c r="X166" s="10" t="n"/>
-      <c r="Y166" s="10" t="n"/>
-      <c r="Z166" s="10" t="n"/>
-      <c r="AA166" s="10" t="n"/>
-      <c r="AB166" s="10" t="n"/>
-      <c r="AC166" s="10" t="n"/>
-      <c r="AD166" s="10" t="n"/>
-      <c r="AE166" s="10" t="n"/>
-      <c r="AF166" s="10" t="n"/>
-      <c r="AG166" s="10" t="n"/>
-      <c r="AH166" s="10" t="n"/>
-      <c r="AI166" s="10" t="n"/>
-      <c r="AJ166" s="10" t="n"/>
-      <c r="AK166" s="11" t="n"/>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="B167" s="27" t="inlineStr">
+      <c r="D168" s="10" t="n"/>
+      <c r="E168" s="10" t="n"/>
+      <c r="F168" s="10" t="n"/>
+      <c r="G168" s="10" t="n"/>
+      <c r="H168" s="10" t="n"/>
+      <c r="I168" s="10" t="n"/>
+      <c r="J168" s="10" t="n"/>
+      <c r="K168" s="10" t="n"/>
+      <c r="L168" s="10" t="n"/>
+      <c r="M168" s="10" t="n"/>
+      <c r="N168" s="10" t="n"/>
+      <c r="O168" s="10" t="n"/>
+      <c r="P168" s="10" t="n"/>
+      <c r="Q168" s="10" t="n"/>
+      <c r="R168" s="10" t="n"/>
+      <c r="S168" s="10" t="n"/>
+      <c r="T168" s="10" t="n"/>
+      <c r="U168" s="10" t="n"/>
+      <c r="V168" s="10" t="n"/>
+      <c r="W168" s="10" t="n"/>
+      <c r="X168" s="10" t="n"/>
+      <c r="Y168" s="10" t="n"/>
+      <c r="Z168" s="10" t="n"/>
+      <c r="AA168" s="10" t="n"/>
+      <c r="AB168" s="10" t="n"/>
+      <c r="AC168" s="10" t="n"/>
+      <c r="AD168" s="10" t="n"/>
+      <c r="AE168" s="10" t="n"/>
+      <c r="AF168" s="10" t="n"/>
+      <c r="AG168" s="10" t="n"/>
+      <c r="AH168" s="10" t="n"/>
+      <c r="AI168" s="10" t="n"/>
+      <c r="AJ168" s="10" t="n"/>
+      <c r="AK168" s="11" t="n"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="B169" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="36" customHeight="1">
-      <c r="C168" s="41" t="inlineStr">
+    <row r="170" ht="36" customHeight="1">
+      <c r="C170" s="41" t="inlineStr">
         <is>
           <t>取得結果を `data` 配列、件数情報を `meta` オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="36" customHeight="1">
-      <c r="C169" s="41" t="inlineStr">
+    <row r="171" ht="36" customHeight="1">
+      <c r="C171" s="41" t="inlineStr">
         <is>
           <t>0件の場合は `data: []` を返し、フロントエンドが ACSMS-MSG-013-001「履歴データが存在しません。」を表示する。</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="B170" s="27" t="inlineStr">
+    <row r="172" ht="18" customHeight="1">
+      <c r="B172" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="C171" s="41" t="inlineStr">
+    <row r="173" ht="18" customHeight="1">
+      <c r="C173" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="36" customHeight="1">
-      <c r="C172" s="41" t="inlineStr">
+    <row r="174" ht="36" customHeight="1">
+      <c r="C174" s="41" t="inlineStr">
         <is>
           <t>本APIは参照系のため操作ログ（`t_log`）の記録は不要。ただしエラー発生時はアプリケーションロガーへ出力する（log_type=3 相当）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="594">
+  <mergeCells count="606">
+    <mergeCell ref="C174:AK174"/>
     <mergeCell ref="AF65:AK65"/>
+    <mergeCell ref="A139:AK139"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D61:L61"/>
@@ -9770,12 +9968,9 @@
     <mergeCell ref="D62:L62"/>
     <mergeCell ref="T68:X68"/>
     <mergeCell ref="D56:L56"/>
-    <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
-    <mergeCell ref="B147:AK147"/>
     <mergeCell ref="Y103:AE103"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="AF91:AK91"/>
     <mergeCell ref="J1:P1"/>
@@ -9790,25 +9985,23 @@
     <mergeCell ref="Q91:S91"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
-    <mergeCell ref="D155:AK155"/>
     <mergeCell ref="Y98:AE98"/>
     <mergeCell ref="M90:P90"/>
     <mergeCell ref="AF86:AK86"/>
     <mergeCell ref="Q106:S106"/>
     <mergeCell ref="Q77:S77"/>
-    <mergeCell ref="B163:AK163"/>
     <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="AF101:AK101"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="B165:AK165"/>
+    <mergeCell ref="B140:AK140"/>
     <mergeCell ref="M85:P85"/>
-    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="D75:L75"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Q109:S109"/>
     <mergeCell ref="M103:P103"/>
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="AF104:AK104"/>
@@ -9830,7 +10023,9 @@
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D89:L89"/>
     <mergeCell ref="AF99:AK99"/>
+    <mergeCell ref="C106:C109"/>
     <mergeCell ref="T76:X76"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="C150:AK150"/>
     <mergeCell ref="D65:L65"/>
@@ -9855,16 +10050,18 @@
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
     <mergeCell ref="T59:X59"/>
+    <mergeCell ref="C35:C104"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="D83:L83"/>
     <mergeCell ref="T89:X89"/>
-    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="Y74:AE74"/>
     <mergeCell ref="D85:L85"/>
+    <mergeCell ref="M109:P109"/>
     <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="C163:AK163"/>
     <mergeCell ref="AF105:AK105"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="Y67:AE67"/>
@@ -9872,18 +10069,19 @@
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
-    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="AF107:AK107"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="D80:L80"/>
+    <mergeCell ref="C105:L105"/>
+    <mergeCell ref="Q54:S54"/>
     <mergeCell ref="D145:AK145"/>
-    <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="Q102:S102"/>
     <mergeCell ref="M104:P104"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="T77:X77"/>
+    <mergeCell ref="D147:AK147"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="B167:AK167"/>
     <mergeCell ref="M106:P106"/>
@@ -9891,7 +10089,6 @@
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="A22:AK22"/>
     <mergeCell ref="M66:P66"/>
-    <mergeCell ref="C104:C107"/>
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="Y87:AE87"/>
@@ -9904,6 +10101,7 @@
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="Y82:AE82"/>
+    <mergeCell ref="D158:AK158"/>
     <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="AF70:AK70"/>
@@ -9922,17 +10120,20 @@
     <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="C166:AK166"/>
-    <mergeCell ref="C160:AK160"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="C141:AK141"/>
+    <mergeCell ref="B111:I111"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="T108:X108"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
     <mergeCell ref="Y72:AE72"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C143:AK143"/>
     <mergeCell ref="M107:P107"/>
     <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="T109:X109"/>
     <mergeCell ref="D35:L35"/>
     <mergeCell ref="T84:X84"/>
     <mergeCell ref="AF34:AK34"/>
@@ -9952,10 +10153,10 @@
     <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="Y65:AE65"/>
     <mergeCell ref="D76:L76"/>
-    <mergeCell ref="B109:I109"/>
     <mergeCell ref="Q85:S85"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="C154:AK154"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="AF80:AK80"/>
     <mergeCell ref="AC29:AE29"/>
@@ -9964,6 +10165,7 @@
     <mergeCell ref="M87:P87"/>
     <mergeCell ref="C168:AK168"/>
     <mergeCell ref="M64:P64"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="C25:L25"/>
@@ -9971,13 +10173,12 @@
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
-    <mergeCell ref="C169:AK169"/>
     <mergeCell ref="M65:P65"/>
     <mergeCell ref="Y78:AE78"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
-    <mergeCell ref="D105:L105"/>
+    <mergeCell ref="B114:I114"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="Y80:AE80"/>
@@ -9986,11 +10187,9 @@
     <mergeCell ref="AF68:AK68"/>
     <mergeCell ref="Y96:AE96"/>
     <mergeCell ref="D107:L107"/>
-    <mergeCell ref="C35:C102"/>
-    <mergeCell ref="B130:I130"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
-    <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="B117:I117"/>
     <mergeCell ref="Y91:AE91"/>
     <mergeCell ref="D102:L102"/>
     <mergeCell ref="M34:P34"/>
@@ -9998,6 +10197,7 @@
     <mergeCell ref="D142:AK142"/>
     <mergeCell ref="C162:AK162"/>
     <mergeCell ref="AF79:AK79"/>
+    <mergeCell ref="B132:I132"/>
     <mergeCell ref="Y106:AE106"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
@@ -10005,20 +10205,19 @@
     <mergeCell ref="D144:AK144"/>
     <mergeCell ref="C164:AK164"/>
     <mergeCell ref="Q101:S101"/>
-    <mergeCell ref="B158:AK158"/>
     <mergeCell ref="D54:L54"/>
-    <mergeCell ref="B112:I112"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="M78:P78"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="B160:AK160"/>
     <mergeCell ref="T56:X56"/>
     <mergeCell ref="T105:X105"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="T99:X99"/>
+    <mergeCell ref="Y109:AE109"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="T107:X107"/>
     <mergeCell ref="T101:X101"/>
@@ -10040,14 +10239,13 @@
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="T64:X64"/>
+    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
-    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
     <mergeCell ref="Y59:AE59"/>
-    <mergeCell ref="B133:I133"/>
     <mergeCell ref="Q92:S92"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="D45:L45"/>
@@ -10062,6 +10260,7 @@
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
+    <mergeCell ref="B135:I135"/>
     <mergeCell ref="Q94:S94"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T33:X33"/>
@@ -10076,18 +10275,19 @@
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="Q105:S105"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="AF100:AK100"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
     <mergeCell ref="D98:L98"/>
     <mergeCell ref="Q107:S107"/>
+    <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF102:AK102"/>
-    <mergeCell ref="C103:L103"/>
     <mergeCell ref="Y64:AE64"/>
-    <mergeCell ref="D140:AK140"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="AF77:AK77"/>
     <mergeCell ref="M99:P99"/>
@@ -10097,7 +10297,9 @@
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T72:X72"/>
     <mergeCell ref="T28:X28"/>
+    <mergeCell ref="B123:I123"/>
     <mergeCell ref="T57:X57"/>
+    <mergeCell ref="B149:AK149"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="D66:L66"/>
     <mergeCell ref="D53:L53"/>
@@ -10111,6 +10313,7 @@
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y75:AE75"/>
     <mergeCell ref="AF88:AK88"/>
+    <mergeCell ref="Q108:S108"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -10130,26 +10333,25 @@
     <mergeCell ref="T85:X85"/>
     <mergeCell ref="Q96:S96"/>
     <mergeCell ref="T60:X60"/>
+    <mergeCell ref="C130:AK130"/>
     <mergeCell ref="D81:L81"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M105:P105"/>
     <mergeCell ref="C159:AK159"/>
-    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="C153:AK153"/>
     <mergeCell ref="M36:P36"/>
-    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="M101:P101"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="C161:AK161"/>
+    <mergeCell ref="AF108:AK108"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
+    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="M100:P100"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="D143:AK143"/>
     <mergeCell ref="T78:X78"/>
-    <mergeCell ref="B170:AK170"/>
     <mergeCell ref="T65:X65"/>
     <mergeCell ref="M102:P102"/>
     <mergeCell ref="Q27:S27"/>
@@ -10158,11 +10360,11 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="B172:AK172"/>
     <mergeCell ref="D92:L92"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="T79:X79"/>
-    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="D67:L67"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
@@ -10174,10 +10376,8 @@
     <mergeCell ref="AF98:AK98"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="D154:AK154"/>
     <mergeCell ref="M95:P95"/>
     <mergeCell ref="M89:P89"/>
-    <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
@@ -10189,8 +10389,10 @@
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="D87:L87"/>
+    <mergeCell ref="D157:AK157"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="AF109:AK109"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="Y71:AE71"/>
     <mergeCell ref="M52:P52"/>
@@ -10205,6 +10407,7 @@
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
+    <mergeCell ref="M108:P108"/>
     <mergeCell ref="D100:L100"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q68:S68"/>
@@ -10212,14 +10415,15 @@
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="Q97:S97"/>
     <mergeCell ref="D77:L77"/>
+    <mergeCell ref="D108:L108"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="Y84:AE84"/>
     <mergeCell ref="D95:L95"/>
+    <mergeCell ref="C155:AK155"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="Y86:AE86"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C157:AK157"/>
     <mergeCell ref="C151:AK151"/>
     <mergeCell ref="D72:L72"/>
     <mergeCell ref="N17:AK17"/>
@@ -10227,6 +10431,7 @@
     <mergeCell ref="M96:P96"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="B120:I120"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="M98:P98"/>
@@ -10247,19 +10452,21 @@
     <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="D90:L90"/>
     <mergeCell ref="AF67:AK67"/>
+    <mergeCell ref="B126:I126"/>
     <mergeCell ref="T95:X95"/>
     <mergeCell ref="Y81:AE81"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
+    <mergeCell ref="C170:AK170"/>
     <mergeCell ref="Q103:S103"/>
     <mergeCell ref="AF62:AK62"/>
-    <mergeCell ref="B115:I115"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Q69:S69"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
     <mergeCell ref="AF64:AK64"/>
+    <mergeCell ref="D103:L103"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="Q98:S98"/>
@@ -10272,6 +10479,7 @@
     <mergeCell ref="M73:P73"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="M60:P60"/>
+    <mergeCell ref="B169:AK169"/>
     <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y94:AE94"/>
@@ -10298,7 +10506,6 @@
     <mergeCell ref="Y107:AE107"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="D106:L106"/>
-    <mergeCell ref="C172:AK172"/>
     <mergeCell ref="D93:L93"/>
     <mergeCell ref="M68:P68"/>
     <mergeCell ref="M92:P92"/>
@@ -10306,13 +10513,15 @@
     <mergeCell ref="C171:AK171"/>
     <mergeCell ref="A31:AK31"/>
     <mergeCell ref="M67:P67"/>
+    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="AF72:AK72"/>
     <mergeCell ref="Q75:S75"/>
+    <mergeCell ref="C173:AK173"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="B118:I118"/>
+    <mergeCell ref="D109:L109"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
@@ -10323,12 +10532,14 @@
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B129:I129"/>
     <mergeCell ref="Q88:S88"/>
+    <mergeCell ref="Y108:AE108"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="B121:I121"/>
     <mergeCell ref="Y95:AE95"/>
+    <mergeCell ref="D146:AK146"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="T93:X93"/>
@@ -10347,9 +10558,6 @@
     <mergeCell ref="M94:P94"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="B124:I124"/>
-    <mergeCell ref="C110:AK110"/>
-    <mergeCell ref="A137:AK137"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>

--- a/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者履歴情報画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-013/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_購読者履歴情報画面_V1.0.xlsx
@@ -13,6 +13,7 @@
     <sheet name="エラー一覧" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="API一覧" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ACSMS-API-013-001" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ACSMS-API-013-002" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1351,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1688,19 +1689,130 @@
       <c r="AF5" s="10" t="n"/>
       <c r="AG5" s="11" t="n"/>
     </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>実装との差分是正（仕様変更ではなく記載漏れの補完）：①レスポンスに実際は含まれている `torikeshi_flg`（取消済フラグ）と `can_torikeshi`（取消可否）をレスポンス項目表へ追記。前者は API-013-002 で取消された行の識別、後者は取消ボタンの活性制御にFE が使用しており、API-013-002 の追加時に本表への追記が漏れていた。②`created_by` の説明とサンプルを実装に合わせて修正。ログインID（例 `ja_honten01`）ではなく、画面操作は `m_account.account_id` の文字列（例 `"539"`）、バッチ実行は `SYSTEM_DENSHI_SYNC` / `SYSTEM_BATCH_NIGHTLY` 等の固定名（#55719 でバッチ実行者名を SYSTEM_* に統一）が入る。③履歴取消API（ACSMS-API-013-002 / `POST /api/v1/dokusya/{dokusya_id}/rireki/{dokusya_rireki_id}/torikeshi`）の節を新規追記。画面設計書 §4 と本書の変更履歴では参照していたが、API 定義そのものが本書に存在しなかった。あわせてエラー一覧に `TORIKESHI_NOT_ALLOWED` を追加。</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="W6" s="17" t="inlineStr"/>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="17" t="inlineStr"/>
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/15</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>実装との差分是正（記載漏れ・誤記の補完）：①増部日/減部日の根拠列の誤記を修正。「`dokusya_kaishi_date` を表示」としていたが、実装（`DokusyaRirekiView.vue` の `zoubuDate()`/`genbuDate()`、dokusya_rireki_record_writing_rules.md §6.2）は `joho_henko_tekiyo_date`（読者情報変更適用日）を根拠にしている。また減部日の「`zenkai_dokusya_busu` が null のとき表示」は誤りで、null 行は増部扱いのため減部日は空欄（`genbuDate()` は `zenkai != null` を要求）。`torikeshi_flg=true` 行は両方常に空欄である旨も追記。②API-013-001 の DataScope 違反時レスポンスの誤記を修正。「HTTP 403 (`DATA_SCOPE_VIOLATION`)」としていたが、実装（`DokusyaService.fetchInScope` → `assertBranchScope`/`assertShitenScope`）は行の存在を秘匿するため HTTP 404 (`NOT_FOUND`) でマスクしており、API-013-002 側の記載（§4.2）と矛盾していた。§4.2・§4.3・レスポンス失敗例を修正し、実装済みの所属支店(`shiten_id`)スコープ（顧客要件2026-07・`assertShitenScope`）を DataScope 説明へ追記。③レスポンス項目表の項目番号が `torikeshi_flg`/`can_torikeshi` 追加時（No.5）にリナンバーされておらず No.62・63 が重複していたのを No.62〜78 に振り直し。</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="W7" s="17" t="inlineStr"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="17" t="inlineStr"/>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="49">
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="R5:V5"/>
+    <mergeCell ref="W6:AA6"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="W5:AA5"/>
     <mergeCell ref="R4:V4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="C4:G4"/>
+    <mergeCell ref="R7:V7"/>
     <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="R6:V6"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="K3:Q3"/>
     <mergeCell ref="W4:AA4"/>
@@ -1708,16 +1820,20 @@
     <mergeCell ref="W3:AA3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="AB7:AG7"/>
     <mergeCell ref="K5:Q5"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W7:AA7"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AB3:AG3"/>
     <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="AB6:AG6"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="AB5:AG5"/>
     <mergeCell ref="W2:AA2"/>
     <mergeCell ref="H4:J4"/>
@@ -1725,6 +1841,7 @@
     <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1897,7 +2014,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2162,7 +2279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2323,7 +2440,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2838,7 +2955,7 @@
       <c r="U13" s="11" t="n"/>
       <c r="V13" s="19" t="inlineStr">
         <is>
-          <t>指定された購読者が見つかりません。</t>
+          <t>指定された購読者が見つかりません。／指定された履歴が見つかりません。</t>
         </is>
       </c>
       <c r="W13" s="10" t="n"/>
@@ -2857,8 +2974,61 @@
       <c r="AJ13" s="10" t="n"/>
       <c r="AK13" s="11" t="n"/>
     </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>TORIKESHI_NOT_ALLOWED</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="11" t="n"/>
+      <c r="V14" s="19" t="inlineStr">
+        <is>
+          <t>取消できないレコードです（紙版・適用日が未来の末尾レコードのみ取消可能。新規・取消済・中間レコード・電子版・適用日到来済みは取消できません）。</t>
+        </is>
+      </c>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="10" t="n"/>
+      <c r="AH14" s="10" t="n"/>
+      <c r="AI14" s="10" t="n"/>
+      <c r="AJ14" s="10" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="54">
     <mergeCell ref="V11:AK11"/>
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="C8:I8"/>
@@ -2881,12 +3051,15 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C14:I14"/>
     <mergeCell ref="J12:U12"/>
     <mergeCell ref="V5:AK5"/>
     <mergeCell ref="V8:AK8"/>
+    <mergeCell ref="V14:AK14"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="V13:AK13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="C10:I10"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J8:U8"/>
@@ -2898,6 +3071,7 @@
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="J5:U5"/>
     <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J14:U14"/>
     <mergeCell ref="J10:U10"/>
     <mergeCell ref="V9:AK9"/>
     <mergeCell ref="A10:B10"/>
@@ -2920,7 +3094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3081,7 +3255,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3252,13 +3426,74 @@
       <c r="AJ6" s="10" t="n"/>
       <c r="AK6" s="11" t="n"/>
     </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>ACSMS-API-013-002</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Torikeshi Dokusya History (赤伝)</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="11" t="n"/>
+      <c r="S7" s="19" t="inlineStr">
+        <is>
+          <t>指定した履歴行を取消する。対象行に `torikeshi_flg` を立て、値を前回値と入れ替えた打ち消し行（赤伝）を追加し、購読者マスタ（`t_dokusya`）を再計算する</t>
+        </is>
+      </c>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n"/>
+      <c r="AB7" s="10" t="n"/>
+      <c r="AC7" s="11" t="n"/>
+      <c r="AD7" s="19" t="inlineStr">
+        <is>
+          <t>/api/v1/dokusya/{dokusya_id}/rireki/{dokusya_rireki_id}/torikeshi</t>
+        </is>
+      </c>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="10" t="n"/>
+      <c r="AH7" s="10" t="n"/>
+      <c r="AI7" s="10" t="n"/>
+      <c r="AJ7" s="10" t="n"/>
+      <c r="AK7" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="29">
     <mergeCell ref="J6:R6"/>
+    <mergeCell ref="C7:I7"/>
     <mergeCell ref="AD5:AK5"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="J7:R7"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="S7:AC7"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD6:AK6"/>
@@ -3275,12 +3510,14 @@
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="J5:R5"/>
+    <mergeCell ref="AD7:AK7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="S5:AC5"/>
     <mergeCell ref="V2:Y3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3292,7 +3529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK174"/>
+  <dimension ref="A1:AK173"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3453,7 +3690,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8062,7 +8299,7 @@
       <c r="AJ93" s="10" t="n"/>
       <c r="AK93" s="11" t="n"/>
     </row>
-    <row r="94" ht="18" customHeight="1">
+    <row r="94" ht="72" customHeight="1">
       <c r="B94" s="31" t="n">
         <v>61</v>
       </c>
@@ -8109,7 +8346,7 @@
       <c r="AE94" s="11" t="n"/>
       <c r="AF94" s="19" t="inlineStr">
         <is>
-          <t>履歴作成者</t>
+          <t>履歴作成者。画面操作は `m_account.account_id`（例 `"539"`）、バッチは `SYSTEM_DENSHI_SYNC` / `SYSTEM_BATCH_NIGHTLY` 等の固定名（#55719）</t>
         </is>
       </c>
       <c r="AG94" s="10" t="n"/>
@@ -8118,14 +8355,14 @@
       <c r="AJ94" s="10" t="n"/>
       <c r="AK94" s="11" t="n"/>
     </row>
-    <row r="95" ht="54" customHeight="1">
+    <row r="95" ht="36" customHeight="1">
       <c r="B95" s="31" t="n">
         <v>62</v>
       </c>
       <c r="C95" s="38" t="n"/>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t>dokusya_shubetsu</t>
+          <t>torikeshi_flg</t>
         </is>
       </c>
       <c r="E95" s="10" t="n"/>
@@ -8138,7 +8375,7 @@
       <c r="L95" s="11" t="n"/>
       <c r="M95" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N95" s="10" t="n"/>
@@ -8165,7 +8402,7 @@
       <c r="AE95" s="11" t="n"/>
       <c r="AF95" s="19" t="inlineStr">
         <is>
-          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）。SCR-013 一覧の 履歴番号 直後に表示</t>
+          <t>取消済フラグ（TRUE=API-013-002 で取消された行。画面では打ち消し線で表示）</t>
         </is>
       </c>
       <c r="AG95" s="10" t="n"/>
@@ -8174,14 +8411,14 @@
       <c r="AJ95" s="10" t="n"/>
       <c r="AK95" s="11" t="n"/>
     </row>
-    <row r="96" ht="18" customHeight="1">
+    <row r="96" ht="36" customHeight="1">
       <c r="B96" s="31" t="n">
         <v>63</v>
       </c>
       <c r="C96" s="38" t="n"/>
       <c r="D96" s="19" t="inlineStr">
         <is>
-          <t>tanka_id</t>
+          <t>can_torikeshi</t>
         </is>
       </c>
       <c r="E96" s="10" t="n"/>
@@ -8194,7 +8431,7 @@
       <c r="L96" s="11" t="n"/>
       <c r="M96" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N96" s="10" t="n"/>
@@ -8212,11 +8449,7 @@
       <c r="V96" s="10" t="n"/>
       <c r="W96" s="10" t="n"/>
       <c r="X96" s="11" t="n"/>
-      <c r="Y96" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y96" s="17" t="inlineStr"/>
       <c r="Z96" s="10" t="n"/>
       <c r="AA96" s="10" t="n"/>
       <c r="AB96" s="10" t="n"/>
@@ -8225,7 +8458,7 @@
       <c r="AE96" s="11" t="n"/>
       <c r="AF96" s="19" t="inlineStr">
         <is>
-          <t>新聞単価ID（m_tanka）※未設定(NULL)あり</t>
+          <t>取消可否（この行に対して API-013-002 を実行できるか。取消ボタンの活性制御に使う）</t>
         </is>
       </c>
       <c r="AG96" s="10" t="n"/>
@@ -8234,14 +8467,14 @@
       <c r="AJ96" s="10" t="n"/>
       <c r="AK96" s="11" t="n"/>
     </row>
-    <row r="97" ht="36" customHeight="1">
+    <row r="97" ht="54" customHeight="1">
       <c r="B97" s="31" t="n">
         <v>64</v>
       </c>
       <c r="C97" s="38" t="n"/>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t>tanka_name</t>
+          <t>dokusya_shubetsu</t>
         </is>
       </c>
       <c r="E97" s="10" t="n"/>
@@ -8254,7 +8487,7 @@
       <c r="L97" s="11" t="n"/>
       <c r="M97" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N97" s="10" t="n"/>
@@ -8272,11 +8505,7 @@
       <c r="V97" s="10" t="n"/>
       <c r="W97" s="10" t="n"/>
       <c r="X97" s="11" t="n"/>
-      <c r="Y97" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y97" s="17" t="inlineStr"/>
       <c r="Z97" s="10" t="n"/>
       <c r="AA97" s="10" t="n"/>
       <c r="AB97" s="10" t="n"/>
@@ -8285,7 +8514,7 @@
       <c r="AE97" s="11" t="n"/>
       <c r="AF97" s="19" t="inlineStr">
         <is>
-          <t>新聞単価名（m_tanka 結合、単価削除済み等は null）。一覧は「単価名 + 半角スペース + 金額」で表示</t>
+          <t>購読種別 ※m_code.code_category='DOKUSYA_SHUBETSU'を参照（1:紙版, 2:電子版, 3:併読）。SCR-013 一覧の 履歴番号 直後に表示</t>
         </is>
       </c>
       <c r="AG97" s="10" t="n"/>
@@ -8294,14 +8523,14 @@
       <c r="AJ97" s="10" t="n"/>
       <c r="AK97" s="11" t="n"/>
     </row>
-    <row r="98" ht="54" customHeight="1">
+    <row r="98" ht="18" customHeight="1">
       <c r="B98" s="31" t="n">
         <v>65</v>
       </c>
       <c r="C98" s="38" t="n"/>
       <c r="D98" s="19" t="inlineStr">
         <is>
-          <t>tanka_kingaku</t>
+          <t>tanka_id</t>
         </is>
       </c>
       <c r="E98" s="10" t="n"/>
@@ -8345,7 +8574,7 @@
       <c r="AE98" s="11" t="n"/>
       <c r="AF98" s="19" t="inlineStr">
         <is>
-          <t>新聞単価の表示金額。JA の税区分(m_ja.zei_kubun)で解決（1:内税→税込 / それ以外→税抜）。単価削除済み等は null</t>
+          <t>新聞単価ID（m_tanka）※未設定(NULL)あり</t>
         </is>
       </c>
       <c r="AG98" s="10" t="n"/>
@@ -8361,7 +8590,7 @@
       <c r="C99" s="38" t="n"/>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t>shiharai_hoho</t>
+          <t>tanka_name</t>
         </is>
       </c>
       <c r="E99" s="10" t="n"/>
@@ -8374,7 +8603,7 @@
       <c r="L99" s="11" t="n"/>
       <c r="M99" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N99" s="10" t="n"/>
@@ -8392,7 +8621,11 @@
       <c r="V99" s="10" t="n"/>
       <c r="W99" s="10" t="n"/>
       <c r="X99" s="11" t="n"/>
-      <c r="Y99" s="17" t="inlineStr"/>
+      <c r="Y99" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z99" s="10" t="n"/>
       <c r="AA99" s="10" t="n"/>
       <c r="AB99" s="10" t="n"/>
@@ -8401,7 +8634,7 @@
       <c r="AE99" s="11" t="n"/>
       <c r="AF99" s="19" t="inlineStr">
         <is>
-          <t>支払い方法 ※m_code.code_category='SHIHARAI_HOHO'を参照</t>
+          <t>新聞単価名（m_tanka 結合、単価削除済み等は null）。一覧は「単価名 + 半角スペース + 金額」で表示</t>
         </is>
       </c>
       <c r="AG99" s="10" t="n"/>
@@ -8410,14 +8643,14 @@
       <c r="AJ99" s="10" t="n"/>
       <c r="AK99" s="11" t="n"/>
     </row>
-    <row r="100" ht="36" customHeight="1">
+    <row r="100" ht="54" customHeight="1">
       <c r="B100" s="31" t="n">
         <v>67</v>
       </c>
       <c r="C100" s="38" t="n"/>
       <c r="D100" s="19" t="inlineStr">
         <is>
-          <t>yubin_kubun</t>
+          <t>tanka_kingaku</t>
         </is>
       </c>
       <c r="E100" s="10" t="n"/>
@@ -8430,7 +8663,7 @@
       <c r="L100" s="11" t="n"/>
       <c r="M100" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N100" s="10" t="n"/>
@@ -8448,7 +8681,11 @@
       <c r="V100" s="10" t="n"/>
       <c r="W100" s="10" t="n"/>
       <c r="X100" s="11" t="n"/>
-      <c r="Y100" s="17" t="inlineStr"/>
+      <c r="Y100" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="Z100" s="10" t="n"/>
       <c r="AA100" s="10" t="n"/>
       <c r="AB100" s="10" t="n"/>
@@ -8457,7 +8694,7 @@
       <c r="AE100" s="11" t="n"/>
       <c r="AF100" s="19" t="inlineStr">
         <is>
-          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
+          <t>新聞単価の表示金額。JA の税区分(m_ja.zei_kubun)で解決（1:内税→税込 / それ以外→税抜）。単価削除済み等は null</t>
         </is>
       </c>
       <c r="AG100" s="10" t="n"/>
@@ -8466,14 +8703,14 @@
       <c r="AJ100" s="10" t="n"/>
       <c r="AK100" s="11" t="n"/>
     </row>
-    <row r="101" ht="18" customHeight="1">
+    <row r="101" ht="36" customHeight="1">
       <c r="B101" s="31" t="n">
         <v>68</v>
       </c>
       <c r="C101" s="38" t="n"/>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t>dokusyaryo_shiharai_cycle</t>
+          <t>shiharai_hoho</t>
         </is>
       </c>
       <c r="E101" s="10" t="n"/>
@@ -8504,11 +8741,7 @@
       <c r="V101" s="10" t="n"/>
       <c r="W101" s="10" t="n"/>
       <c r="X101" s="11" t="n"/>
-      <c r="Y101" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y101" s="17" t="inlineStr"/>
       <c r="Z101" s="10" t="n"/>
       <c r="AA101" s="10" t="n"/>
       <c r="AB101" s="10" t="n"/>
@@ -8517,7 +8750,7 @@
       <c r="AE101" s="11" t="n"/>
       <c r="AF101" s="19" t="inlineStr">
         <is>
-          <t>購読料支払サイクル（月数 1〜12、未設定は null）</t>
+          <t>支払い方法 ※m_code.code_category='SHIHARAI_HOHO'を参照</t>
         </is>
       </c>
       <c r="AG101" s="10" t="n"/>
@@ -8533,7 +8766,7 @@
       <c r="C102" s="38" t="n"/>
       <c r="D102" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>yubin_kubun</t>
         </is>
       </c>
       <c r="E102" s="10" t="n"/>
@@ -8573,7 +8806,7 @@
       <c r="AE102" s="11" t="n"/>
       <c r="AF102" s="19" t="inlineStr">
         <is>
-          <t>備考（取消時は取消理由を記録・空文字許容）。一覧の最終データ列</t>
+          <t>郵送区分 ※m_code.code_category='YUBIN_KUBUN'を参照（0:空, 1:郵送）</t>
         </is>
       </c>
       <c r="AG102" s="10" t="n"/>
@@ -8582,14 +8815,14 @@
       <c r="AJ102" s="10" t="n"/>
       <c r="AK102" s="11" t="n"/>
     </row>
-    <row r="103" ht="72" customHeight="1">
+    <row r="103" ht="18" customHeight="1">
       <c r="B103" s="31" t="n">
         <v>70</v>
       </c>
       <c r="C103" s="38" t="n"/>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t>denshi_dokusya_shubetsu</t>
+          <t>dokusyaryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E103" s="10" t="n"/>
@@ -8633,7 +8866,7 @@
       <c r="AE103" s="11" t="n"/>
       <c r="AF103" s="19" t="inlineStr">
         <is>
-          <t>電子版読者種別 ※m_code.code_category='DENSHI_DOKUSYA_SHUBETSU'を参照（0:無料, 1:有料）。紙版は電子版連携が無いため null。SCR-013 一覧の 購読種別 直後に表示</t>
+          <t>購読料支払サイクル（月数 1〜12、未設定は null）</t>
         </is>
       </c>
       <c r="AG103" s="10" t="n"/>
@@ -8642,14 +8875,14 @@
       <c r="AJ103" s="10" t="n"/>
       <c r="AK103" s="11" t="n"/>
     </row>
-    <row r="104" ht="72" customHeight="1">
+    <row r="104" ht="36" customHeight="1">
       <c r="B104" s="31" t="n">
         <v>71</v>
       </c>
-      <c r="C104" s="39" t="n"/>
+      <c r="C104" s="38" t="n"/>
       <c r="D104" s="19" t="inlineStr">
         <is>
-          <t>denshi_shonin_status</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E104" s="10" t="n"/>
@@ -8662,7 +8895,7 @@
       <c r="L104" s="11" t="n"/>
       <c r="M104" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N104" s="10" t="n"/>
@@ -8680,11 +8913,7 @@
       <c r="V104" s="10" t="n"/>
       <c r="W104" s="10" t="n"/>
       <c r="X104" s="11" t="n"/>
-      <c r="Y104" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="Y104" s="17" t="inlineStr"/>
       <c r="Z104" s="10" t="n"/>
       <c r="AA104" s="10" t="n"/>
       <c r="AB104" s="10" t="n"/>
@@ -8693,7 +8922,7 @@
       <c r="AE104" s="11" t="n"/>
       <c r="AF104" s="19" t="inlineStr">
         <is>
-          <t>電子申込承認ステータス（0:未承認, 1:承認済み, 2:否認）。m_code ではなく電子版連携の状態から導出。Web申込以外（紙版等）は null。SCR-013 一覧の 電子版読者種別 直後に表示</t>
+          <t>備考（取消時は取消理由を記録・空文字許容）。一覧の最終データ列</t>
         </is>
       </c>
       <c r="AG104" s="10" t="n"/>
@@ -8702,16 +8931,16 @@
       <c r="AJ104" s="10" t="n"/>
       <c r="AK104" s="11" t="n"/>
     </row>
-    <row r="105" ht="18" customHeight="1">
+    <row r="105" ht="72" customHeight="1">
       <c r="B105" s="31" t="n">
         <v>72</v>
       </c>
-      <c r="C105" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="n"/>
+      <c r="C105" s="38" t="n"/>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>denshi_dokusya_shubetsu</t>
+        </is>
+      </c>
       <c r="E105" s="10" t="n"/>
       <c r="F105" s="10" t="n"/>
       <c r="G105" s="10" t="n"/>
@@ -8722,7 +8951,7 @@
       <c r="L105" s="11" t="n"/>
       <c r="M105" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N105" s="10" t="n"/>
@@ -8742,7 +8971,7 @@
       <c r="X105" s="11" t="n"/>
       <c r="Y105" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z105" s="10" t="n"/>
@@ -8753,7 +8982,7 @@
       <c r="AE105" s="11" t="n"/>
       <c r="AF105" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>電子版読者種別 ※m_code.code_category='DENSHI_DOKUSYA_SHUBETSU'を参照（0:無料, 1:有料）。紙版は電子版連携が無いため null。SCR-013 一覧の 購読種別 直後に表示</t>
         </is>
       </c>
       <c r="AG105" s="10" t="n"/>
@@ -8762,14 +8991,14 @@
       <c r="AJ105" s="10" t="n"/>
       <c r="AK105" s="11" t="n"/>
     </row>
-    <row r="106" ht="18" customHeight="1">
+    <row r="106" ht="72" customHeight="1">
       <c r="B106" s="31" t="n">
         <v>73</v>
       </c>
-      <c r="C106" s="37" t="n"/>
+      <c r="C106" s="39" t="n"/>
       <c r="D106" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>denshi_shonin_status</t>
         </is>
       </c>
       <c r="E106" s="10" t="n"/>
@@ -8802,7 +9031,7 @@
       <c r="X106" s="11" t="n"/>
       <c r="Y106" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z106" s="10" t="n"/>
@@ -8813,7 +9042,7 @@
       <c r="AE106" s="11" t="n"/>
       <c r="AF106" s="19" t="inlineStr">
         <is>
-          <t>該当件数（履歴データ全体）</t>
+          <t>電子申込承認ステータス（0:未承認, 1:承認済み, 2:否認）。m_code ではなく電子版連携の状態から導出。Web申込以外（紙版等）は null。SCR-013 一覧の 電子版読者種別 直後に表示</t>
         </is>
       </c>
       <c r="AG106" s="10" t="n"/>
@@ -8826,12 +9055,12 @@
       <c r="B107" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="C107" s="38" t="n"/>
-      <c r="D107" s="19" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
+      <c r="C107" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="n"/>
       <c r="E107" s="10" t="n"/>
       <c r="F107" s="10" t="n"/>
       <c r="G107" s="10" t="n"/>
@@ -8842,7 +9071,7 @@
       <c r="L107" s="11" t="n"/>
       <c r="M107" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N107" s="10" t="n"/>
@@ -8873,7 +9102,7 @@
       <c r="AE107" s="11" t="n"/>
       <c r="AF107" s="19" t="inlineStr">
         <is>
-          <t>現在のページ</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG107" s="10" t="n"/>
@@ -8886,10 +9115,10 @@
       <c r="B108" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="C108" s="38" t="n"/>
+      <c r="C108" s="37" t="n"/>
       <c r="D108" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E108" s="10" t="n"/>
@@ -8933,7 +9162,7 @@
       <c r="AE108" s="11" t="n"/>
       <c r="AF108" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>該当件数（履歴データ全体）</t>
         </is>
       </c>
       <c r="AG108" s="10" t="n"/>
@@ -8946,10 +9175,10 @@
       <c r="B109" s="31" t="n">
         <v>76</v>
       </c>
-      <c r="C109" s="39" t="n"/>
+      <c r="C109" s="38" t="n"/>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E109" s="10" t="n"/>
@@ -8993,7 +9222,7 @@
       <c r="AE109" s="11" t="n"/>
       <c r="AF109" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>現在のページ</t>
         </is>
       </c>
       <c r="AG109" s="10" t="n"/>
@@ -9002,64 +9231,184 @@
       <c r="AJ109" s="10" t="n"/>
       <c r="AK109" s="11" t="n"/>
     </row>
-    <row r="110" ht="19.5" customHeight="1"/>
-    <row r="111" ht="19.5" customHeight="1">
-      <c r="B111" s="40" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="B110" s="31" t="n">
+        <v>77</v>
+      </c>
+      <c r="C110" s="38" t="n"/>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="11" t="n"/>
+      <c r="M110" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N110" s="10" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="11" t="n"/>
+      <c r="Q110" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="11" t="n"/>
+      <c r="T110" s="17" t="inlineStr"/>
+      <c r="U110" s="10" t="n"/>
+      <c r="V110" s="10" t="n"/>
+      <c r="W110" s="10" t="n"/>
+      <c r="X110" s="11" t="n"/>
+      <c r="Y110" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z110" s="10" t="n"/>
+      <c r="AA110" s="10" t="n"/>
+      <c r="AB110" s="10" t="n"/>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="19" t="inlineStr">
+        <is>
+          <t>1ページあたりの件数</t>
+        </is>
+      </c>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="10" t="n"/>
+      <c r="AK110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="31" t="n">
+        <v>78</v>
+      </c>
+      <c r="C111" s="39" t="n"/>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="n"/>
+      <c r="F111" s="10" t="n"/>
+      <c r="G111" s="10" t="n"/>
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="10" t="n"/>
+      <c r="J111" s="10" t="n"/>
+      <c r="K111" s="10" t="n"/>
+      <c r="L111" s="11" t="n"/>
+      <c r="M111" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N111" s="10" t="n"/>
+      <c r="O111" s="10" t="n"/>
+      <c r="P111" s="11" t="n"/>
+      <c r="Q111" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R111" s="10" t="n"/>
+      <c r="S111" s="11" t="n"/>
+      <c r="T111" s="17" t="inlineStr"/>
+      <c r="U111" s="10" t="n"/>
+      <c r="V111" s="10" t="n"/>
+      <c r="W111" s="10" t="n"/>
+      <c r="X111" s="11" t="n"/>
+      <c r="Y111" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z111" s="10" t="n"/>
+      <c r="AA111" s="10" t="n"/>
+      <c r="AB111" s="10" t="n"/>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="10" t="n"/>
+      <c r="AK111" s="11" t="n"/>
+    </row>
+    <row r="112" ht="19.5" customHeight="1"/>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="B113" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="C112" s="19" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="C114" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/dokusya/1/rireki?page=1&amp;per_page=20&amp;sort_by=rireki_no&amp;sort_order=desc</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
-      <c r="P112" s="10" t="n"/>
-      <c r="Q112" s="10" t="n"/>
-      <c r="R112" s="10" t="n"/>
-      <c r="S112" s="10" t="n"/>
-      <c r="T112" s="10" t="n"/>
-      <c r="U112" s="10" t="n"/>
-      <c r="V112" s="10" t="n"/>
-      <c r="W112" s="10" t="n"/>
-      <c r="X112" s="10" t="n"/>
-      <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AA112" s="10" t="n"/>
-      <c r="AB112" s="10" t="n"/>
-      <c r="AC112" s="10" t="n"/>
-      <c r="AD112" s="10" t="n"/>
-      <c r="AE112" s="10" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
-      <c r="AI112" s="10" t="n"/>
-      <c r="AJ112" s="10" t="n"/>
-      <c r="AK112" s="11" t="n"/>
-    </row>
-    <row r="114" ht="19.5" customHeight="1">
-      <c r="B114" s="40" t="inlineStr">
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="B116" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="409" customHeight="1">
-      <c r="C115" s="19" t="inlineStr">
+    <row r="117" ht="409" customHeight="1">
+      <c r="C117" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -9133,7 +9482,9 @@
       "hikiotoshi_koza_no": "1234567",
       "hikiotoshi_koza_meigi": "ヤマダタロウ",
       "created_at": "2026-04-01T10:00:00Z",
-      "created_by": "ja_honten01"
+      "created_by": "539",
+      "torikeshi_flg": false,
+      "can_torikeshi": true
     }
   ],
   "meta": {
@@ -9145,50 +9496,50 @@
 }</t>
         </is>
       </c>
-      <c r="D115" s="10" t="n"/>
-      <c r="E115" s="10" t="n"/>
-      <c r="F115" s="10" t="n"/>
-      <c r="G115" s="10" t="n"/>
-      <c r="H115" s="10" t="n"/>
-      <c r="I115" s="10" t="n"/>
-      <c r="J115" s="10" t="n"/>
-      <c r="K115" s="10" t="n"/>
-      <c r="L115" s="10" t="n"/>
-      <c r="M115" s="10" t="n"/>
-      <c r="N115" s="10" t="n"/>
-      <c r="O115" s="10" t="n"/>
-      <c r="P115" s="10" t="n"/>
-      <c r="Q115" s="10" t="n"/>
-      <c r="R115" s="10" t="n"/>
-      <c r="S115" s="10" t="n"/>
-      <c r="T115" s="10" t="n"/>
-      <c r="U115" s="10" t="n"/>
-      <c r="V115" s="10" t="n"/>
-      <c r="W115" s="10" t="n"/>
-      <c r="X115" s="10" t="n"/>
-      <c r="Y115" s="10" t="n"/>
-      <c r="Z115" s="10" t="n"/>
-      <c r="AA115" s="10" t="n"/>
-      <c r="AB115" s="10" t="n"/>
-      <c r="AC115" s="10" t="n"/>
-      <c r="AD115" s="10" t="n"/>
-      <c r="AE115" s="10" t="n"/>
-      <c r="AF115" s="10" t="n"/>
-      <c r="AG115" s="10" t="n"/>
-      <c r="AH115" s="10" t="n"/>
-      <c r="AI115" s="10" t="n"/>
-      <c r="AJ115" s="10" t="n"/>
-      <c r="AK115" s="11" t="n"/>
-    </row>
-    <row r="117" ht="19.5" customHeight="1">
-      <c r="B117" s="40" t="inlineStr">
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="B119" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="72" customHeight="1">
-      <c r="C118" s="19" t="inlineStr">
+    <row r="120" ht="72" customHeight="1">
+      <c r="C120" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "BAD_REQUEST",
@@ -9196,50 +9547,50 @@
 }</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n"/>
-      <c r="E118" s="10" t="n"/>
-      <c r="F118" s="10" t="n"/>
-      <c r="G118" s="10" t="n"/>
-      <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="n"/>
-      <c r="J118" s="10" t="n"/>
-      <c r="K118" s="10" t="n"/>
-      <c r="L118" s="10" t="n"/>
-      <c r="M118" s="10" t="n"/>
-      <c r="N118" s="10" t="n"/>
-      <c r="O118" s="10" t="n"/>
-      <c r="P118" s="10" t="n"/>
-      <c r="Q118" s="10" t="n"/>
-      <c r="R118" s="10" t="n"/>
-      <c r="S118" s="10" t="n"/>
-      <c r="T118" s="10" t="n"/>
-      <c r="U118" s="10" t="n"/>
-      <c r="V118" s="10" t="n"/>
-      <c r="W118" s="10" t="n"/>
-      <c r="X118" s="10" t="n"/>
-      <c r="Y118" s="10" t="n"/>
-      <c r="Z118" s="10" t="n"/>
-      <c r="AA118" s="10" t="n"/>
-      <c r="AB118" s="10" t="n"/>
-      <c r="AC118" s="10" t="n"/>
-      <c r="AD118" s="10" t="n"/>
-      <c r="AE118" s="10" t="n"/>
-      <c r="AF118" s="10" t="n"/>
-      <c r="AG118" s="10" t="n"/>
-      <c r="AH118" s="10" t="n"/>
-      <c r="AI118" s="10" t="n"/>
-      <c r="AJ118" s="10" t="n"/>
-      <c r="AK118" s="11" t="n"/>
-    </row>
-    <row r="120" ht="19.5" customHeight="1">
-      <c r="B120" s="40" t="inlineStr">
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="10" t="n"/>
+      <c r="K120" s="10" t="n"/>
+      <c r="L120" s="10" t="n"/>
+      <c r="M120" s="10" t="n"/>
+      <c r="N120" s="10" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="10" t="n"/>
+      <c r="Q120" s="10" t="n"/>
+      <c r="R120" s="10" t="n"/>
+      <c r="S120" s="10" t="n"/>
+      <c r="T120" s="10" t="n"/>
+      <c r="U120" s="10" t="n"/>
+      <c r="V120" s="10" t="n"/>
+      <c r="W120" s="10" t="n"/>
+      <c r="X120" s="10" t="n"/>
+      <c r="Y120" s="10" t="n"/>
+      <c r="Z120" s="10" t="n"/>
+      <c r="AA120" s="10" t="n"/>
+      <c r="AB120" s="10" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="10" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="10" t="n"/>
+      <c r="AK120" s="11" t="n"/>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="B122" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="72" customHeight="1">
-      <c r="C121" s="19" t="inlineStr">
+    <row r="123" ht="72" customHeight="1">
+      <c r="C123" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -9247,50 +9598,50 @@
 }</t>
         </is>
       </c>
-      <c r="D121" s="10" t="n"/>
-      <c r="E121" s="10" t="n"/>
-      <c r="F121" s="10" t="n"/>
-      <c r="G121" s="10" t="n"/>
-      <c r="H121" s="10" t="n"/>
-      <c r="I121" s="10" t="n"/>
-      <c r="J121" s="10" t="n"/>
-      <c r="K121" s="10" t="n"/>
-      <c r="L121" s="10" t="n"/>
-      <c r="M121" s="10" t="n"/>
-      <c r="N121" s="10" t="n"/>
-      <c r="O121" s="10" t="n"/>
-      <c r="P121" s="10" t="n"/>
-      <c r="Q121" s="10" t="n"/>
-      <c r="R121" s="10" t="n"/>
-      <c r="S121" s="10" t="n"/>
-      <c r="T121" s="10" t="n"/>
-      <c r="U121" s="10" t="n"/>
-      <c r="V121" s="10" t="n"/>
-      <c r="W121" s="10" t="n"/>
-      <c r="X121" s="10" t="n"/>
-      <c r="Y121" s="10" t="n"/>
-      <c r="Z121" s="10" t="n"/>
-      <c r="AA121" s="10" t="n"/>
-      <c r="AB121" s="10" t="n"/>
-      <c r="AC121" s="10" t="n"/>
-      <c r="AD121" s="10" t="n"/>
-      <c r="AE121" s="10" t="n"/>
-      <c r="AF121" s="10" t="n"/>
-      <c r="AG121" s="10" t="n"/>
-      <c r="AH121" s="10" t="n"/>
-      <c r="AI121" s="10" t="n"/>
-      <c r="AJ121" s="10" t="n"/>
-      <c r="AK121" s="11" t="n"/>
-    </row>
-    <row r="123" ht="19.5" customHeight="1">
-      <c r="B123" s="40" t="inlineStr">
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="10" t="n"/>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
+      <c r="H123" s="10" t="n"/>
+      <c r="I123" s="10" t="n"/>
+      <c r="J123" s="10" t="n"/>
+      <c r="K123" s="10" t="n"/>
+      <c r="L123" s="10" t="n"/>
+      <c r="M123" s="10" t="n"/>
+      <c r="N123" s="10" t="n"/>
+      <c r="O123" s="10" t="n"/>
+      <c r="P123" s="10" t="n"/>
+      <c r="Q123" s="10" t="n"/>
+      <c r="R123" s="10" t="n"/>
+      <c r="S123" s="10" t="n"/>
+      <c r="T123" s="10" t="n"/>
+      <c r="U123" s="10" t="n"/>
+      <c r="V123" s="10" t="n"/>
+      <c r="W123" s="10" t="n"/>
+      <c r="X123" s="10" t="n"/>
+      <c r="Y123" s="10" t="n"/>
+      <c r="Z123" s="10" t="n"/>
+      <c r="AA123" s="10" t="n"/>
+      <c r="AB123" s="10" t="n"/>
+      <c r="AC123" s="10" t="n"/>
+      <c r="AD123" s="10" t="n"/>
+      <c r="AE123" s="10" t="n"/>
+      <c r="AF123" s="10" t="n"/>
+      <c r="AG123" s="10" t="n"/>
+      <c r="AH123" s="10" t="n"/>
+      <c r="AI123" s="10" t="n"/>
+      <c r="AJ123" s="10" t="n"/>
+      <c r="AK123" s="11" t="n"/>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="B125" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="72" customHeight="1">
-      <c r="C124" s="19" t="inlineStr">
+    <row r="126" ht="72" customHeight="1">
+      <c r="C126" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -9298,101 +9649,50 @@
 }</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n"/>
-      <c r="E124" s="10" t="n"/>
-      <c r="F124" s="10" t="n"/>
-      <c r="G124" s="10" t="n"/>
-      <c r="H124" s="10" t="n"/>
-      <c r="I124" s="10" t="n"/>
-      <c r="J124" s="10" t="n"/>
-      <c r="K124" s="10" t="n"/>
-      <c r="L124" s="10" t="n"/>
-      <c r="M124" s="10" t="n"/>
-      <c r="N124" s="10" t="n"/>
-      <c r="O124" s="10" t="n"/>
-      <c r="P124" s="10" t="n"/>
-      <c r="Q124" s="10" t="n"/>
-      <c r="R124" s="10" t="n"/>
-      <c r="S124" s="10" t="n"/>
-      <c r="T124" s="10" t="n"/>
-      <c r="U124" s="10" t="n"/>
-      <c r="V124" s="10" t="n"/>
-      <c r="W124" s="10" t="n"/>
-      <c r="X124" s="10" t="n"/>
-      <c r="Y124" s="10" t="n"/>
-      <c r="Z124" s="10" t="n"/>
-      <c r="AA124" s="10" t="n"/>
-      <c r="AB124" s="10" t="n"/>
-      <c r="AC124" s="10" t="n"/>
-      <c r="AD124" s="10" t="n"/>
-      <c r="AE124" s="10" t="n"/>
-      <c r="AF124" s="10" t="n"/>
-      <c r="AG124" s="10" t="n"/>
-      <c r="AH124" s="10" t="n"/>
-      <c r="AI124" s="10" t="n"/>
-      <c r="AJ124" s="10" t="n"/>
-      <c r="AK124" s="11" t="n"/>
-    </row>
-    <row r="126" ht="19.5" customHeight="1">
-      <c r="B126" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 403 Data Scope Violation）</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="72" customHeight="1">
-      <c r="C127" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "DATA_SCOPE_VIOLATION",
-  "message": "このデータへのアクセス権限がありません。"
-}</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="n"/>
-      <c r="E127" s="10" t="n"/>
-      <c r="F127" s="10" t="n"/>
-      <c r="G127" s="10" t="n"/>
-      <c r="H127" s="10" t="n"/>
-      <c r="I127" s="10" t="n"/>
-      <c r="J127" s="10" t="n"/>
-      <c r="K127" s="10" t="n"/>
-      <c r="L127" s="10" t="n"/>
-      <c r="M127" s="10" t="n"/>
-      <c r="N127" s="10" t="n"/>
-      <c r="O127" s="10" t="n"/>
-      <c r="P127" s="10" t="n"/>
-      <c r="Q127" s="10" t="n"/>
-      <c r="R127" s="10" t="n"/>
-      <c r="S127" s="10" t="n"/>
-      <c r="T127" s="10" t="n"/>
-      <c r="U127" s="10" t="n"/>
-      <c r="V127" s="10" t="n"/>
-      <c r="W127" s="10" t="n"/>
-      <c r="X127" s="10" t="n"/>
-      <c r="Y127" s="10" t="n"/>
-      <c r="Z127" s="10" t="n"/>
-      <c r="AA127" s="10" t="n"/>
-      <c r="AB127" s="10" t="n"/>
-      <c r="AC127" s="10" t="n"/>
-      <c r="AD127" s="10" t="n"/>
-      <c r="AE127" s="10" t="n"/>
-      <c r="AF127" s="10" t="n"/>
-      <c r="AG127" s="10" t="n"/>
-      <c r="AH127" s="10" t="n"/>
-      <c r="AI127" s="10" t="n"/>
-      <c r="AJ127" s="10" t="n"/>
-      <c r="AK127" s="11" t="n"/>
-    </row>
-    <row r="129" ht="19.5" customHeight="1">
-      <c r="B129" s="40" t="inlineStr">
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="10" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="n"/>
+      <c r="I126" s="10" t="n"/>
+      <c r="J126" s="10" t="n"/>
+      <c r="K126" s="10" t="n"/>
+      <c r="L126" s="10" t="n"/>
+      <c r="M126" s="10" t="n"/>
+      <c r="N126" s="10" t="n"/>
+      <c r="O126" s="10" t="n"/>
+      <c r="P126" s="10" t="n"/>
+      <c r="Q126" s="10" t="n"/>
+      <c r="R126" s="10" t="n"/>
+      <c r="S126" s="10" t="n"/>
+      <c r="T126" s="10" t="n"/>
+      <c r="U126" s="10" t="n"/>
+      <c r="V126" s="10" t="n"/>
+      <c r="W126" s="10" t="n"/>
+      <c r="X126" s="10" t="n"/>
+      <c r="Y126" s="10" t="n"/>
+      <c r="Z126" s="10" t="n"/>
+      <c r="AA126" s="10" t="n"/>
+      <c r="AB126" s="10" t="n"/>
+      <c r="AC126" s="10" t="n"/>
+      <c r="AD126" s="10" t="n"/>
+      <c r="AE126" s="10" t="n"/>
+      <c r="AF126" s="10" t="n"/>
+      <c r="AG126" s="10" t="n"/>
+      <c r="AH126" s="10" t="n"/>
+      <c r="AI126" s="10" t="n"/>
+      <c r="AJ126" s="10" t="n"/>
+      <c r="AK126" s="11" t="n"/>
+    </row>
+    <row r="128" ht="19.5" customHeight="1">
+      <c r="B128" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="72" customHeight="1">
-      <c r="C130" s="19" t="inlineStr">
+    <row r="129" ht="72" customHeight="1">
+      <c r="C129" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -9400,50 +9700,50 @@
 }</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n"/>
-      <c r="E130" s="10" t="n"/>
-      <c r="F130" s="10" t="n"/>
-      <c r="G130" s="10" t="n"/>
-      <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="n"/>
-      <c r="J130" s="10" t="n"/>
-      <c r="K130" s="10" t="n"/>
-      <c r="L130" s="10" t="n"/>
-      <c r="M130" s="10" t="n"/>
-      <c r="N130" s="10" t="n"/>
-      <c r="O130" s="10" t="n"/>
-      <c r="P130" s="10" t="n"/>
-      <c r="Q130" s="10" t="n"/>
-      <c r="R130" s="10" t="n"/>
-      <c r="S130" s="10" t="n"/>
-      <c r="T130" s="10" t="n"/>
-      <c r="U130" s="10" t="n"/>
-      <c r="V130" s="10" t="n"/>
-      <c r="W130" s="10" t="n"/>
-      <c r="X130" s="10" t="n"/>
-      <c r="Y130" s="10" t="n"/>
-      <c r="Z130" s="10" t="n"/>
-      <c r="AA130" s="10" t="n"/>
-      <c r="AB130" s="10" t="n"/>
-      <c r="AC130" s="10" t="n"/>
-      <c r="AD130" s="10" t="n"/>
-      <c r="AE130" s="10" t="n"/>
-      <c r="AF130" s="10" t="n"/>
-      <c r="AG130" s="10" t="n"/>
-      <c r="AH130" s="10" t="n"/>
-      <c r="AI130" s="10" t="n"/>
-      <c r="AJ130" s="10" t="n"/>
-      <c r="AK130" s="11" t="n"/>
-    </row>
-    <row r="132" ht="19.5" customHeight="1">
-      <c r="B132" s="40" t="inlineStr">
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="10" t="n"/>
+      <c r="I129" s="10" t="n"/>
+      <c r="J129" s="10" t="n"/>
+      <c r="K129" s="10" t="n"/>
+      <c r="L129" s="10" t="n"/>
+      <c r="M129" s="10" t="n"/>
+      <c r="N129" s="10" t="n"/>
+      <c r="O129" s="10" t="n"/>
+      <c r="P129" s="10" t="n"/>
+      <c r="Q129" s="10" t="n"/>
+      <c r="R129" s="10" t="n"/>
+      <c r="S129" s="10" t="n"/>
+      <c r="T129" s="10" t="n"/>
+      <c r="U129" s="10" t="n"/>
+      <c r="V129" s="10" t="n"/>
+      <c r="W129" s="10" t="n"/>
+      <c r="X129" s="10" t="n"/>
+      <c r="Y129" s="10" t="n"/>
+      <c r="Z129" s="10" t="n"/>
+      <c r="AA129" s="10" t="n"/>
+      <c r="AB129" s="10" t="n"/>
+      <c r="AC129" s="10" t="n"/>
+      <c r="AD129" s="10" t="n"/>
+      <c r="AE129" s="10" t="n"/>
+      <c r="AF129" s="10" t="n"/>
+      <c r="AG129" s="10" t="n"/>
+      <c r="AH129" s="10" t="n"/>
+      <c r="AI129" s="10" t="n"/>
+      <c r="AJ129" s="10" t="n"/>
+      <c r="AK129" s="11" t="n"/>
+    </row>
+    <row r="131" ht="19.5" customHeight="1">
+      <c r="B131" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 429 Too Many Requests）</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="72" customHeight="1">
-      <c r="C133" s="19" t="inlineStr">
+    <row r="132" ht="72" customHeight="1">
+      <c r="C132" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "TOO_MANY_REQUESTS",
@@ -9451,50 +9751,50 @@
 }</t>
         </is>
       </c>
-      <c r="D133" s="10" t="n"/>
-      <c r="E133" s="10" t="n"/>
-      <c r="F133" s="10" t="n"/>
-      <c r="G133" s="10" t="n"/>
-      <c r="H133" s="10" t="n"/>
-      <c r="I133" s="10" t="n"/>
-      <c r="J133" s="10" t="n"/>
-      <c r="K133" s="10" t="n"/>
-      <c r="L133" s="10" t="n"/>
-      <c r="M133" s="10" t="n"/>
-      <c r="N133" s="10" t="n"/>
-      <c r="O133" s="10" t="n"/>
-      <c r="P133" s="10" t="n"/>
-      <c r="Q133" s="10" t="n"/>
-      <c r="R133" s="10" t="n"/>
-      <c r="S133" s="10" t="n"/>
-      <c r="T133" s="10" t="n"/>
-      <c r="U133" s="10" t="n"/>
-      <c r="V133" s="10" t="n"/>
-      <c r="W133" s="10" t="n"/>
-      <c r="X133" s="10" t="n"/>
-      <c r="Y133" s="10" t="n"/>
-      <c r="Z133" s="10" t="n"/>
-      <c r="AA133" s="10" t="n"/>
-      <c r="AB133" s="10" t="n"/>
-      <c r="AC133" s="10" t="n"/>
-      <c r="AD133" s="10" t="n"/>
-      <c r="AE133" s="10" t="n"/>
-      <c r="AF133" s="10" t="n"/>
-      <c r="AG133" s="10" t="n"/>
-      <c r="AH133" s="10" t="n"/>
-      <c r="AI133" s="10" t="n"/>
-      <c r="AJ133" s="10" t="n"/>
-      <c r="AK133" s="11" t="n"/>
-    </row>
-    <row r="135" ht="19.5" customHeight="1">
-      <c r="B135" s="40" t="inlineStr">
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="10" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="10" t="n"/>
+      <c r="J132" s="10" t="n"/>
+      <c r="K132" s="10" t="n"/>
+      <c r="L132" s="10" t="n"/>
+      <c r="M132" s="10" t="n"/>
+      <c r="N132" s="10" t="n"/>
+      <c r="O132" s="10" t="n"/>
+      <c r="P132" s="10" t="n"/>
+      <c r="Q132" s="10" t="n"/>
+      <c r="R132" s="10" t="n"/>
+      <c r="S132" s="10" t="n"/>
+      <c r="T132" s="10" t="n"/>
+      <c r="U132" s="10" t="n"/>
+      <c r="V132" s="10" t="n"/>
+      <c r="W132" s="10" t="n"/>
+      <c r="X132" s="10" t="n"/>
+      <c r="Y132" s="10" t="n"/>
+      <c r="Z132" s="10" t="n"/>
+      <c r="AA132" s="10" t="n"/>
+      <c r="AB132" s="10" t="n"/>
+      <c r="AC132" s="10" t="n"/>
+      <c r="AD132" s="10" t="n"/>
+      <c r="AE132" s="10" t="n"/>
+      <c r="AF132" s="10" t="n"/>
+      <c r="AG132" s="10" t="n"/>
+      <c r="AH132" s="10" t="n"/>
+      <c r="AI132" s="10" t="n"/>
+      <c r="AJ132" s="10" t="n"/>
+      <c r="AK132" s="11" t="n"/>
+    </row>
+    <row r="134" ht="19.5" customHeight="1">
+      <c r="B134" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="72" customHeight="1">
-      <c r="C136" s="19" t="inlineStr">
+    <row r="135" ht="72" customHeight="1">
+      <c r="C135" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -9502,186 +9802,193 @@
 }</t>
         </is>
       </c>
-      <c r="D136" s="10" t="n"/>
-      <c r="E136" s="10" t="n"/>
-      <c r="F136" s="10" t="n"/>
-      <c r="G136" s="10" t="n"/>
-      <c r="H136" s="10" t="n"/>
-      <c r="I136" s="10" t="n"/>
-      <c r="J136" s="10" t="n"/>
-      <c r="K136" s="10" t="n"/>
-      <c r="L136" s="10" t="n"/>
-      <c r="M136" s="10" t="n"/>
-      <c r="N136" s="10" t="n"/>
-      <c r="O136" s="10" t="n"/>
-      <c r="P136" s="10" t="n"/>
-      <c r="Q136" s="10" t="n"/>
-      <c r="R136" s="10" t="n"/>
-      <c r="S136" s="10" t="n"/>
-      <c r="T136" s="10" t="n"/>
-      <c r="U136" s="10" t="n"/>
-      <c r="V136" s="10" t="n"/>
-      <c r="W136" s="10" t="n"/>
-      <c r="X136" s="10" t="n"/>
-      <c r="Y136" s="10" t="n"/>
-      <c r="Z136" s="10" t="n"/>
-      <c r="AA136" s="10" t="n"/>
-      <c r="AB136" s="10" t="n"/>
-      <c r="AC136" s="10" t="n"/>
-      <c r="AD136" s="10" t="n"/>
-      <c r="AE136" s="10" t="n"/>
-      <c r="AF136" s="10" t="n"/>
-      <c r="AG136" s="10" t="n"/>
-      <c r="AH136" s="10" t="n"/>
-      <c r="AI136" s="10" t="n"/>
-      <c r="AJ136" s="10" t="n"/>
-      <c r="AK136" s="11" t="n"/>
-    </row>
-    <row r="138" ht="19.5" customHeight="1"/>
-    <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="27" t="inlineStr">
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="10" t="n"/>
+      <c r="F135" s="10" t="n"/>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="10" t="n"/>
+      <c r="I135" s="10" t="n"/>
+      <c r="J135" s="10" t="n"/>
+      <c r="K135" s="10" t="n"/>
+      <c r="L135" s="10" t="n"/>
+      <c r="M135" s="10" t="n"/>
+      <c r="N135" s="10" t="n"/>
+      <c r="O135" s="10" t="n"/>
+      <c r="P135" s="10" t="n"/>
+      <c r="Q135" s="10" t="n"/>
+      <c r="R135" s="10" t="n"/>
+      <c r="S135" s="10" t="n"/>
+      <c r="T135" s="10" t="n"/>
+      <c r="U135" s="10" t="n"/>
+      <c r="V135" s="10" t="n"/>
+      <c r="W135" s="10" t="n"/>
+      <c r="X135" s="10" t="n"/>
+      <c r="Y135" s="10" t="n"/>
+      <c r="Z135" s="10" t="n"/>
+      <c r="AA135" s="10" t="n"/>
+      <c r="AB135" s="10" t="n"/>
+      <c r="AC135" s="10" t="n"/>
+      <c r="AD135" s="10" t="n"/>
+      <c r="AE135" s="10" t="n"/>
+      <c r="AF135" s="10" t="n"/>
+      <c r="AG135" s="10" t="n"/>
+      <c r="AH135" s="10" t="n"/>
+      <c r="AI135" s="10" t="n"/>
+      <c r="AJ135" s="10" t="n"/>
+      <c r="AK135" s="11" t="n"/>
+    </row>
+    <row r="137" ht="19.5" customHeight="1"/>
+    <row r="138" ht="19.5" customHeight="1">
+      <c r="A138" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="B140" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="C140" s="41" t="inlineStr">
+        <is>
+          <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="C141" s="41" t="inlineStr">
-        <is>
-          <t>パスパラメータの検証：</t>
+      <c r="D141" s="41" t="inlineStr">
+        <is>
+          <t>`dokusya_id`：数値型、必須。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="D142" s="41" t="inlineStr">
-        <is>
-          <t>`dokusya_id`：数値型、必須。</t>
+      <c r="C142" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="C143" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
+      <c r="D143" s="41" t="inlineStr">
+        <is>
+          <t>`page`：数値型、`&gt;= 1`。省略時 `1`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1">
       <c r="D144" s="41" t="inlineStr">
         <is>
-          <t>`page`：数値型、`&gt;= 1`。省略時 `1`。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="36" customHeight="1">
+          <t>`per_page`：数値型、`1 &lt;= per_page &lt;= 100`。省略時 `20`（機能定義 3.1 デフォルト 20、最大 100）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="54" customHeight="1">
       <c r="D145" s="41" t="inlineStr">
         <is>
-          <t>`per_page`：数値型、`1 &lt;= per_page &lt;= 100`。省略時 `20`（機能定義 3.1 デフォルト 20、最大 100）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="54" customHeight="1">
+          <t>`sort_by`：許可リスト = `{rireki_no, dokusya_kaishi_date, joho_henko_tekiyo_date, created_at}`。省略時 `rireki_no`。許可リスト外の値はバリデーションエラー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="36" customHeight="1">
       <c r="D146" s="41" t="inlineStr">
         <is>
-          <t>`sort_by`：許可リスト = `{rireki_no, dokusya_kaishi_date, joho_henko_tekiyo_date, created_at}`。省略時 `rireki_no`。許可リスト外の値はバリデーションエラー。</t>
+          <t>`sort_order`：許可リスト = `{asc, desc}`。省略時 `desc`（機能定義 1.2 最新レコードを先頭）。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="36" customHeight="1">
-      <c r="D147" s="41" t="inlineStr">
-        <is>
-          <t>`sort_order`：許可リスト = `{asc, desc}`。省略時 `desc`（機能定義 1.2 最新レコードを先頭）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="36" customHeight="1">
-      <c r="C148" s="41" t="inlineStr">
+      <c r="C147" s="41" t="inlineStr">
         <is>
           <t>バリデーション失敗時：HTTP 400 (`BAD_REQUEST` / `VALIDATION_ERROR`)</t>
         </is>
       </c>
     </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="B148" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="B149" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C149" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="C150" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="C151" s="41" t="inlineStr">
         <is>
-          <t>未認証の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="18" customHeight="1">
+          <t>必要権限: `dokusya.view`</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="36" customHeight="1">
       <c r="C152" s="41" t="inlineStr">
         <is>
-          <t>必要権限: `dokusya.view`</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="36" customHeight="1">
+          <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN（seeder.md §3 マトリクス No.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
       <c r="C153" s="41" t="inlineStr">
         <is>
-          <t>該当権限保持ロール: CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN（seeder.md §3 マトリクス No.2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="18" customHeight="1">
+          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="54" customHeight="1">
       <c r="C154" s="41" t="inlineStr">
         <is>
-          <t>権限不足の場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="C155" s="41" t="inlineStr">
-        <is>
-          <t>DataScope（account_concept.md ※1）:</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="36" customHeight="1">
+          <t>DataScope（account_concept.md ※1。実装は共通ヘルパ `fetchInScope` → `assertBranchScope` / `assertShitenScope`）:</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="36" customHeight="1">
+      <c r="D155" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI: `ja_id = user.ja_id`（自中央会のレコードのみ。管轄JAの読者は閲覧不可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
       <c r="D156" s="41" t="inlineStr">
         <is>
-          <t>CHUOKAI: `ja_id = user.ja_id`（自中央会のレコードのみ。管轄JAの読者は閲覧不可）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="18" customHeight="1">
+          <t>JA_HONTEN: `ja_id = user.ja_id`（自JAのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="36" customHeight="1">
       <c r="D157" s="41" t="inlineStr">
         <is>
-          <t>JA_HONTEN: `ja_id = user.ja_id`（自JAのみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="36" customHeight="1">
+          <t>JA_KANRI_SHITEN: `ja_id = user.ja_id AND kanri_shiten_id = user.kanri_shiten_id`（自管理支店のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="54" customHeight="1">
       <c r="D158" s="41" t="inlineStr">
         <is>
-          <t>JA_KANRI_SHITEN: `ja_id = user.ja_id AND kanri_shiten_id = user.kanri_shiten_id`（自管理支店のみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="36" customHeight="1">
+          <t>所属支店(`user.shiten_id`)設定済みの JA_KANRI_SHITEN アカウント（顧客要件2026-07）: 上記に加え `shiten_id = user.shiten_id` まで絞り込む（account_concept.md「所属支店による追加制限・制限①」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="90" customHeight="1">
       <c r="C159" s="41" t="inlineStr">
         <is>
-          <t>DataScope違反（他JAまたは他管理支店のレコードへのアクセス）の場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>DataScope違反（他JA・他管理支店・他所属支店のレコードへのアクセス）の場合：HTTP 404 (`NOT_FOUND`)。`fetchInScope` はスコープ外を `NotFoundException` として投げ、行の存在を秘匿するため 403 ではなく 404 でマスクする（API-013-002 §4.2 と同じ挙動）。エラー一覧の `DATA_SCOPE_VIOLATION` は共通カタログ掲載の一般エラーコードで、本API では実際には発生しない。</t>
         </is>
       </c>
     </row>
@@ -9746,29 +10053,22 @@
       <c r="AJ162" s="10" t="n"/>
       <c r="AK162" s="11" t="n"/>
     </row>
-    <row r="163" ht="18" customHeight="1">
+    <row r="163" ht="54" customHeight="1">
       <c r="C163" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="36" customHeight="1">
-      <c r="C164" s="41" t="inlineStr">
-        <is>
-          <t>ja_id / kanri_shiten_id が DataScope と一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="B165" s="27" t="inlineStr">
+          <t>レコードが存在しない場合、または ja_id / kanri_shiten_id / shiten_id が DataScope と一致しない場合：いずれも HTTP 404 (`NOT_FOUND`)（§4.2 参照 — 範囲外は 403 ではなく 404 でマスクする）</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="B164" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="108" customHeight="1">
-      <c r="C166" s="42" t="inlineStr">
+    <row r="165" ht="108" customHeight="1">
+      <c r="C165" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM t_dokusya_rireki
@@ -9778,50 +10078,50 @@
   AND (:user_kanri_shiten_id IS NULL OR kanri_shiten_id = :user_kanri_shiten_id)</t>
         </is>
       </c>
-      <c r="D166" s="10" t="n"/>
-      <c r="E166" s="10" t="n"/>
-      <c r="F166" s="10" t="n"/>
-      <c r="G166" s="10" t="n"/>
-      <c r="H166" s="10" t="n"/>
-      <c r="I166" s="10" t="n"/>
-      <c r="J166" s="10" t="n"/>
-      <c r="K166" s="10" t="n"/>
-      <c r="L166" s="10" t="n"/>
-      <c r="M166" s="10" t="n"/>
-      <c r="N166" s="10" t="n"/>
-      <c r="O166" s="10" t="n"/>
-      <c r="P166" s="10" t="n"/>
-      <c r="Q166" s="10" t="n"/>
-      <c r="R166" s="10" t="n"/>
-      <c r="S166" s="10" t="n"/>
-      <c r="T166" s="10" t="n"/>
-      <c r="U166" s="10" t="n"/>
-      <c r="V166" s="10" t="n"/>
-      <c r="W166" s="10" t="n"/>
-      <c r="X166" s="10" t="n"/>
-      <c r="Y166" s="10" t="n"/>
-      <c r="Z166" s="10" t="n"/>
-      <c r="AA166" s="10" t="n"/>
-      <c r="AB166" s="10" t="n"/>
-      <c r="AC166" s="10" t="n"/>
-      <c r="AD166" s="10" t="n"/>
-      <c r="AE166" s="10" t="n"/>
-      <c r="AF166" s="10" t="n"/>
-      <c r="AG166" s="10" t="n"/>
-      <c r="AH166" s="10" t="n"/>
-      <c r="AI166" s="10" t="n"/>
-      <c r="AJ166" s="10" t="n"/>
-      <c r="AK166" s="11" t="n"/>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="B167" s="27" t="inlineStr">
+      <c r="D165" s="10" t="n"/>
+      <c r="E165" s="10" t="n"/>
+      <c r="F165" s="10" t="n"/>
+      <c r="G165" s="10" t="n"/>
+      <c r="H165" s="10" t="n"/>
+      <c r="I165" s="10" t="n"/>
+      <c r="J165" s="10" t="n"/>
+      <c r="K165" s="10" t="n"/>
+      <c r="L165" s="10" t="n"/>
+      <c r="M165" s="10" t="n"/>
+      <c r="N165" s="10" t="n"/>
+      <c r="O165" s="10" t="n"/>
+      <c r="P165" s="10" t="n"/>
+      <c r="Q165" s="10" t="n"/>
+      <c r="R165" s="10" t="n"/>
+      <c r="S165" s="10" t="n"/>
+      <c r="T165" s="10" t="n"/>
+      <c r="U165" s="10" t="n"/>
+      <c r="V165" s="10" t="n"/>
+      <c r="W165" s="10" t="n"/>
+      <c r="X165" s="10" t="n"/>
+      <c r="Y165" s="10" t="n"/>
+      <c r="Z165" s="10" t="n"/>
+      <c r="AA165" s="10" t="n"/>
+      <c r="AB165" s="10" t="n"/>
+      <c r="AC165" s="10" t="n"/>
+      <c r="AD165" s="10" t="n"/>
+      <c r="AE165" s="10" t="n"/>
+      <c r="AF165" s="10" t="n"/>
+      <c r="AG165" s="10" t="n"/>
+      <c r="AH165" s="10" t="n"/>
+      <c r="AI165" s="10" t="n"/>
+      <c r="AJ165" s="10" t="n"/>
+      <c r="AK165" s="11" t="n"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="B166" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="409" customHeight="1">
-      <c r="C168" s="42" t="inlineStr">
+    <row r="167" ht="409" customHeight="1">
+      <c r="C167" s="42" t="inlineStr">
         <is>
           <t>SELECT
   r.dokusya_rireki_id, r.dokusya_id, r.rireki_no,
@@ -9875,88 +10175,86 @@
 LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D168" s="10" t="n"/>
-      <c r="E168" s="10" t="n"/>
-      <c r="F168" s="10" t="n"/>
-      <c r="G168" s="10" t="n"/>
-      <c r="H168" s="10" t="n"/>
-      <c r="I168" s="10" t="n"/>
-      <c r="J168" s="10" t="n"/>
-      <c r="K168" s="10" t="n"/>
-      <c r="L168" s="10" t="n"/>
-      <c r="M168" s="10" t="n"/>
-      <c r="N168" s="10" t="n"/>
-      <c r="O168" s="10" t="n"/>
-      <c r="P168" s="10" t="n"/>
-      <c r="Q168" s="10" t="n"/>
-      <c r="R168" s="10" t="n"/>
-      <c r="S168" s="10" t="n"/>
-      <c r="T168" s="10" t="n"/>
-      <c r="U168" s="10" t="n"/>
-      <c r="V168" s="10" t="n"/>
-      <c r="W168" s="10" t="n"/>
-      <c r="X168" s="10" t="n"/>
-      <c r="Y168" s="10" t="n"/>
-      <c r="Z168" s="10" t="n"/>
-      <c r="AA168" s="10" t="n"/>
-      <c r="AB168" s="10" t="n"/>
-      <c r="AC168" s="10" t="n"/>
-      <c r="AD168" s="10" t="n"/>
-      <c r="AE168" s="10" t="n"/>
-      <c r="AF168" s="10" t="n"/>
-      <c r="AG168" s="10" t="n"/>
-      <c r="AH168" s="10" t="n"/>
-      <c r="AI168" s="10" t="n"/>
-      <c r="AJ168" s="10" t="n"/>
-      <c r="AK168" s="11" t="n"/>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="B169" s="27" t="inlineStr">
+      <c r="D167" s="10" t="n"/>
+      <c r="E167" s="10" t="n"/>
+      <c r="F167" s="10" t="n"/>
+      <c r="G167" s="10" t="n"/>
+      <c r="H167" s="10" t="n"/>
+      <c r="I167" s="10" t="n"/>
+      <c r="J167" s="10" t="n"/>
+      <c r="K167" s="10" t="n"/>
+      <c r="L167" s="10" t="n"/>
+      <c r="M167" s="10" t="n"/>
+      <c r="N167" s="10" t="n"/>
+      <c r="O167" s="10" t="n"/>
+      <c r="P167" s="10" t="n"/>
+      <c r="Q167" s="10" t="n"/>
+      <c r="R167" s="10" t="n"/>
+      <c r="S167" s="10" t="n"/>
+      <c r="T167" s="10" t="n"/>
+      <c r="U167" s="10" t="n"/>
+      <c r="V167" s="10" t="n"/>
+      <c r="W167" s="10" t="n"/>
+      <c r="X167" s="10" t="n"/>
+      <c r="Y167" s="10" t="n"/>
+      <c r="Z167" s="10" t="n"/>
+      <c r="AA167" s="10" t="n"/>
+      <c r="AB167" s="10" t="n"/>
+      <c r="AC167" s="10" t="n"/>
+      <c r="AD167" s="10" t="n"/>
+      <c r="AE167" s="10" t="n"/>
+      <c r="AF167" s="10" t="n"/>
+      <c r="AG167" s="10" t="n"/>
+      <c r="AH167" s="10" t="n"/>
+      <c r="AI167" s="10" t="n"/>
+      <c r="AJ167" s="10" t="n"/>
+      <c r="AK167" s="11" t="n"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="B168" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
+      <c r="C169" s="41" t="inlineStr">
+        <is>
+          <t>取得結果を `data` 配列、件数情報を `meta` オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="36" customHeight="1">
       <c r="C170" s="41" t="inlineStr">
         <is>
-          <t>取得結果を `data` 配列、件数情報を `meta` オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="36" customHeight="1">
-      <c r="C171" s="41" t="inlineStr">
-        <is>
           <t>0件の場合は `data: []` を返し、フロントエンドが ACSMS-MSG-013-001「履歴データが存在しません。」を表示する。</t>
         </is>
       </c>
     </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="B171" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="B172" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="18" customHeight="1">
+      <c r="C172" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="36" customHeight="1">
       <c r="C173" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="36" customHeight="1">
-      <c r="C174" s="41" t="inlineStr">
-        <is>
           <t>本APIは参照系のため操作ログ（`t_log`）の記録は不要。ただしエラー発生時はアプリケーションロガーへ出力する（log_type=3 相当）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="606">
-    <mergeCell ref="C174:AK174"/>
+  <mergeCells count="616">
     <mergeCell ref="AF65:AK65"/>
-    <mergeCell ref="A139:AK139"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D61:L61"/>
@@ -9979,12 +10277,15 @@
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="M88:P88"/>
     <mergeCell ref="M82:P82"/>
+    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF84:AK84"/>
     <mergeCell ref="Q104:S104"/>
+    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q91:S91"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="D155:AK155"/>
     <mergeCell ref="Y98:AE98"/>
     <mergeCell ref="M90:P90"/>
     <mergeCell ref="AF86:AK86"/>
@@ -9995,8 +10296,6 @@
     <mergeCell ref="AF101:AK101"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="B165:AK165"/>
-    <mergeCell ref="B140:AK140"/>
     <mergeCell ref="M85:P85"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="D75:L75"/>
@@ -10007,6 +10306,7 @@
     <mergeCell ref="AF104:AK104"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y66:AE66"/>
+    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
@@ -10020,12 +10320,11 @@
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="AF81:AK81"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D89:L89"/>
     <mergeCell ref="AF99:AK99"/>
-    <mergeCell ref="C106:C109"/>
     <mergeCell ref="T76:X76"/>
-    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="C150:AK150"/>
     <mergeCell ref="D65:L65"/>
@@ -10046,14 +10345,15 @@
     <mergeCell ref="T87:X87"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="B166:AK166"/>
     <mergeCell ref="AF94:AK94"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
     <mergeCell ref="T59:X59"/>
-    <mergeCell ref="C35:C104"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="D83:L83"/>
     <mergeCell ref="T89:X89"/>
+    <mergeCell ref="B168:AK168"/>
     <mergeCell ref="T88:X88"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
@@ -10072,18 +10372,15 @@
     <mergeCell ref="AF107:AK107"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="D80:L80"/>
-    <mergeCell ref="C105:L105"/>
+    <mergeCell ref="D145:AK145"/>
     <mergeCell ref="Q54:S54"/>
-    <mergeCell ref="D145:AK145"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="Q102:S102"/>
     <mergeCell ref="M104:P104"/>
     <mergeCell ref="Q64:S64"/>
     <mergeCell ref="T77:X77"/>
-    <mergeCell ref="D147:AK147"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B167:AK167"/>
     <mergeCell ref="M106:P106"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="T35:X35"/>
@@ -10092,6 +10389,7 @@
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="Y87:AE87"/>
+    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="AF75:AK75"/>
     <mergeCell ref="Y89:AE89"/>
     <mergeCell ref="Q57:S57"/>
@@ -10102,7 +10400,6 @@
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="Y82:AE82"/>
     <mergeCell ref="D158:AK158"/>
-    <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="AF70:AK70"/>
     <mergeCell ref="T96:X96"/>
@@ -10115,25 +10412,26 @@
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="T98:X98"/>
+    <mergeCell ref="C165:AK165"/>
     <mergeCell ref="D86:L86"/>
     <mergeCell ref="M61:P61"/>
+    <mergeCell ref="B134:I134"/>
     <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="C166:AK166"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
-    <mergeCell ref="C141:AK141"/>
-    <mergeCell ref="B111:I111"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="T108:X108"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
+    <mergeCell ref="AF110:AK110"/>
     <mergeCell ref="Y72:AE72"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C143:AK143"/>
     <mergeCell ref="M107:P107"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="T109:X109"/>
+    <mergeCell ref="B164:AK164"/>
+    <mergeCell ref="B139:AK139"/>
     <mergeCell ref="D35:L35"/>
     <mergeCell ref="T84:X84"/>
     <mergeCell ref="AF34:AK34"/>
@@ -10163,22 +10461,24 @@
     <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="T106:X106"/>
     <mergeCell ref="M87:P87"/>
-    <mergeCell ref="C168:AK168"/>
     <mergeCell ref="M64:P64"/>
-    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C167:AK167"/>
+    <mergeCell ref="A138:AK138"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
+    <mergeCell ref="C169:AK169"/>
     <mergeCell ref="M65:P65"/>
     <mergeCell ref="Y78:AE78"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
-    <mergeCell ref="B114:I114"/>
+    <mergeCell ref="D105:L105"/>
+    <mergeCell ref="T111:X111"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="Y80:AE80"/>
@@ -10186,24 +10486,21 @@
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF68:AK68"/>
     <mergeCell ref="Y96:AE96"/>
-    <mergeCell ref="D107:L107"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q84:S84"/>
-    <mergeCell ref="B117:I117"/>
     <mergeCell ref="Y91:AE91"/>
     <mergeCell ref="D102:L102"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="M83:P83"/>
-    <mergeCell ref="D142:AK142"/>
     <mergeCell ref="C162:AK162"/>
     <mergeCell ref="AF79:AK79"/>
-    <mergeCell ref="B132:I132"/>
     <mergeCell ref="Y106:AE106"/>
     <mergeCell ref="M49:P49"/>
+    <mergeCell ref="B119:I119"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="Y93:AE93"/>
+    <mergeCell ref="C107:L107"/>
     <mergeCell ref="D144:AK144"/>
-    <mergeCell ref="C164:AK164"/>
     <mergeCell ref="Q101:S101"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
@@ -10223,6 +10520,7 @@
     <mergeCell ref="T101:X101"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="D57:L57"/>
+    <mergeCell ref="Y111:AE111"/>
     <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="Q79:S79"/>
     <mergeCell ref="Y61:AE61"/>
@@ -10230,21 +10528,25 @@
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="AF74:AK74"/>
     <mergeCell ref="Y104:AE104"/>
+    <mergeCell ref="B122:I122"/>
     <mergeCell ref="Q81:S81"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
+    <mergeCell ref="B148:AK148"/>
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="T62:X62"/>
+    <mergeCell ref="Q110:S110"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="T64:X64"/>
-    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D110:L110"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M84:P84"/>
+    <mergeCell ref="C132:AK132"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="Q92:S92"/>
     <mergeCell ref="Y34:AE34"/>
@@ -10260,7 +10562,6 @@
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
-    <mergeCell ref="B135:I135"/>
     <mergeCell ref="Q94:S94"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T33:X33"/>
@@ -10275,17 +10576,16 @@
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="Q105:S105"/>
-    <mergeCell ref="C112:AK112"/>
+    <mergeCell ref="T110:X110"/>
     <mergeCell ref="AF100:AK100"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
     <mergeCell ref="D98:L98"/>
     <mergeCell ref="Q107:S107"/>
-    <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
-    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="AF102:AK102"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
@@ -10297,9 +10597,9 @@
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T72:X72"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B123:I123"/>
+    <mergeCell ref="D141:AK141"/>
     <mergeCell ref="T57:X57"/>
-    <mergeCell ref="B149:AK149"/>
+    <mergeCell ref="C140:AK140"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="D66:L66"/>
     <mergeCell ref="D53:L53"/>
@@ -10333,7 +10633,6 @@
     <mergeCell ref="T85:X85"/>
     <mergeCell ref="Q96:S96"/>
     <mergeCell ref="T60:X60"/>
-    <mergeCell ref="C130:AK130"/>
     <mergeCell ref="D81:L81"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M105:P105"/>
@@ -10346,11 +10645,11 @@
     <mergeCell ref="AF108:AK108"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
-    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="M100:P100"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="D143:AK143"/>
     <mergeCell ref="T78:X78"/>
     <mergeCell ref="T65:X65"/>
     <mergeCell ref="M102:P102"/>
@@ -10360,7 +10659,6 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="T80:X80"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="B172:AK172"/>
     <mergeCell ref="D92:L92"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
@@ -10372,13 +10670,17 @@
     <mergeCell ref="D94:L94"/>
     <mergeCell ref="AF96:AK96"/>
     <mergeCell ref="D69:L69"/>
+    <mergeCell ref="Y110:AE110"/>
     <mergeCell ref="Y85:AE85"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="AF98:AK98"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="M95:P95"/>
     <mergeCell ref="M89:P89"/>
+    <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="Q111:S111"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="AC24:AE24"/>
@@ -10391,6 +10693,7 @@
     <mergeCell ref="D87:L87"/>
     <mergeCell ref="D157:AK157"/>
     <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="B171:AK171"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF109:AK109"/>
     <mergeCell ref="AF47:AK47"/>
@@ -10398,9 +10701,11 @@
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="D82:L82"/>
     <mergeCell ref="Y58:AE58"/>
+    <mergeCell ref="M110:P110"/>
     <mergeCell ref="T104:X104"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
+    <mergeCell ref="AF111:AK111"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="Y73:AE73"/>
     <mergeCell ref="J15:M15"/>
@@ -10419,7 +10724,8 @@
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="Y84:AE84"/>
     <mergeCell ref="D95:L95"/>
-    <mergeCell ref="C155:AK155"/>
+    <mergeCell ref="C108:C111"/>
+    <mergeCell ref="B125:I125"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="Y86:AE86"/>
     <mergeCell ref="N18:AK18"/>
@@ -10431,7 +10737,7 @@
     <mergeCell ref="M96:P96"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="AF29:AK29"/>
-    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="M111:P111"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="M98:P98"/>
@@ -10452,9 +10758,9 @@
     <mergeCell ref="Y79:AE79"/>
     <mergeCell ref="D90:L90"/>
     <mergeCell ref="AF67:AK67"/>
-    <mergeCell ref="B126:I126"/>
     <mergeCell ref="T95:X95"/>
     <mergeCell ref="Y81:AE81"/>
+    <mergeCell ref="B113:I113"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
@@ -10477,9 +10783,9 @@
     <mergeCell ref="M79:P79"/>
     <mergeCell ref="Y92:AE92"/>
     <mergeCell ref="M73:P73"/>
+    <mergeCell ref="B128:I128"/>
     <mergeCell ref="B14:I20"/>
     <mergeCell ref="M60:P60"/>
-    <mergeCell ref="B169:AK169"/>
     <mergeCell ref="Q87:S87"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y94:AE94"/>
@@ -10506,14 +10812,15 @@
     <mergeCell ref="Y107:AE107"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="D106:L106"/>
+    <mergeCell ref="C35:C106"/>
+    <mergeCell ref="C172:AK172"/>
     <mergeCell ref="D93:L93"/>
     <mergeCell ref="M68:P68"/>
     <mergeCell ref="M92:P92"/>
     <mergeCell ref="M55:P55"/>
-    <mergeCell ref="C171:AK171"/>
     <mergeCell ref="A31:AK31"/>
     <mergeCell ref="M67:P67"/>
-    <mergeCell ref="C121:AK121"/>
+    <mergeCell ref="B116:I116"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="AF72:AK72"/>
     <mergeCell ref="Q75:S75"/>
@@ -10525,14 +10832,15 @@
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
+    <mergeCell ref="D111:L111"/>
     <mergeCell ref="M81:P81"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="C135:AK135"/>
     <mergeCell ref="D104:L104"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="T91:X91"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B129:I129"/>
     <mergeCell ref="Q88:S88"/>
     <mergeCell ref="Y108:AE108"/>
     <mergeCell ref="Q26:S26"/>
@@ -10544,6 +10852,7 @@
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="T93:X93"/>
     <mergeCell ref="AF83:AK83"/>
+    <mergeCell ref="B131:I131"/>
     <mergeCell ref="Q90:S90"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
@@ -10557,10 +10866,1797 @@
     <mergeCell ref="D59:L59"/>
     <mergeCell ref="M94:P94"/>
     <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK70"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="4.25" customWidth="1" min="1" max="1"/>
+    <col width="4.25" customWidth="1" min="2" max="2"/>
+    <col width="4.25" customWidth="1" min="3" max="3"/>
+    <col width="4.25" customWidth="1" min="4" max="4"/>
+    <col width="4.25" customWidth="1" min="5" max="5"/>
+    <col width="4.25" customWidth="1" min="6" max="6"/>
+    <col width="4.25" customWidth="1" min="7" max="7"/>
+    <col width="4.25" customWidth="1" min="8" max="8"/>
+    <col width="4.25" customWidth="1" min="9" max="9"/>
+    <col width="4.25" customWidth="1" min="10" max="10"/>
+    <col width="4.25" customWidth="1" min="11" max="11"/>
+    <col width="4.25" customWidth="1" min="12" max="12"/>
+    <col width="4.25" customWidth="1" min="13" max="13"/>
+    <col width="4.25" customWidth="1" min="14" max="14"/>
+    <col width="4.25" customWidth="1" min="15" max="15"/>
+    <col width="4.25" customWidth="1" min="16" max="16"/>
+    <col width="4.25" customWidth="1" min="17" max="17"/>
+    <col width="4.25" customWidth="1" min="18" max="18"/>
+    <col width="4.25" customWidth="1" min="19" max="19"/>
+    <col width="4.25" customWidth="1" min="20" max="20"/>
+    <col width="4.25" customWidth="1" min="21" max="21"/>
+    <col width="4.25" customWidth="1" min="22" max="22"/>
+    <col width="4.25" customWidth="1" min="23" max="23"/>
+    <col width="4.25" customWidth="1" min="24" max="24"/>
+    <col width="4.25" customWidth="1" min="25" max="25"/>
+    <col width="4.25" customWidth="1" min="26" max="26"/>
+    <col width="4.25" customWidth="1" min="27" max="27"/>
+    <col width="4.25" customWidth="1" min="28" max="28"/>
+    <col width="4.25" customWidth="1" min="29" max="29"/>
+    <col width="4.25" customWidth="1" min="30" max="30"/>
+    <col width="4.25" customWidth="1" min="31" max="31"/>
+    <col width="4.25" customWidth="1" min="32" max="32"/>
+    <col width="4.25" customWidth="1" min="33" max="33"/>
+    <col width="4.25" customWidth="1" min="34" max="34"/>
+    <col width="4.25" customWidth="1" min="35" max="35"/>
+    <col width="4.25" customWidth="1" min="36" max="36"/>
+    <col width="4.25" customWidth="1" min="37" max="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>システム・アプリケーション名</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="10" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="16" t="inlineStr">
+        <is>
+          <t>ドキュメント</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="n"/>
+      <c r="L1" s="10" t="n"/>
+      <c r="M1" s="10" t="n"/>
+      <c r="N1" s="10" t="n"/>
+      <c r="O1" s="10" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="16" t="inlineStr">
+        <is>
+          <t>シート名</t>
+        </is>
+      </c>
+      <c r="R1" s="10" t="n"/>
+      <c r="S1" s="10" t="n"/>
+      <c r="T1" s="10" t="n"/>
+      <c r="U1" s="11" t="n"/>
+      <c r="V1" s="16" t="inlineStr">
+        <is>
+          <t>作成日</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="n"/>
+      <c r="X1" s="10" t="n"/>
+      <c r="Y1" s="11" t="n"/>
+      <c r="Z1" s="16" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="n"/>
+      <c r="AB1" s="10" t="n"/>
+      <c r="AC1" s="11" t="n"/>
+      <c r="AD1" s="16" t="inlineStr">
+        <is>
+          <t>更新日</t>
+        </is>
+      </c>
+      <c r="AE1" s="10" t="n"/>
+      <c r="AF1" s="10" t="n"/>
+      <c r="AG1" s="11" t="n"/>
+      <c r="AH1" s="16" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="AI1" s="10" t="n"/>
+      <c r="AJ1" s="10" t="n"/>
+      <c r="AK1" s="11" t="n"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>クラウド版購読者管理システム</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="20" t="inlineStr">
+        <is>
+          <t>API設計書</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="n"/>
+      <c r="L2" s="21" t="n"/>
+      <c r="M2" s="21" t="n"/>
+      <c r="N2" s="21" t="n"/>
+      <c r="O2" s="21" t="n"/>
+      <c r="P2" s="22" t="n"/>
+      <c r="Q2" s="20" t="inlineStr">
+        <is>
+          <t>ACSMS-API-013-002</t>
+        </is>
+      </c>
+      <c r="R2" s="21" t="n"/>
+      <c r="S2" s="21" t="n"/>
+      <c r="T2" s="21" t="n"/>
+      <c r="U2" s="22" t="n"/>
+      <c r="V2" s="23" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="W2" s="21" t="n"/>
+      <c r="X2" s="21" t="n"/>
+      <c r="Y2" s="22" t="n"/>
+      <c r="Z2" s="20" t="inlineStr">
+        <is>
+          <t>Nguyen Duyen Manh</t>
+        </is>
+      </c>
+      <c r="AA2" s="21" t="n"/>
+      <c r="AB2" s="21" t="n"/>
+      <c r="AC2" s="22" t="n"/>
+      <c r="AD2" s="23" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="AE2" s="21" t="n"/>
+      <c r="AF2" s="21" t="n"/>
+      <c r="AG2" s="22" t="n"/>
+      <c r="AH2" s="20" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="AI2" s="21" t="n"/>
+      <c r="AJ2" s="21" t="n"/>
+      <c r="AK2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="24" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="26" t="n"/>
+      <c r="J3" s="24" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="26" t="n"/>
+      <c r="Q3" s="24" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="26" t="n"/>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="26" t="n"/>
+      <c r="Z3" s="24" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="26" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="26" t="n"/>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="26" t="n"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1"/>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>1.概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1"/>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>API名</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Torikeshi Dokusya History (赤伝)</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n"/>
+      <c r="AB7" s="10" t="n"/>
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="10" t="n"/>
+      <c r="AH7" s="10" t="n"/>
+      <c r="AI7" s="10" t="n"/>
+      <c r="AJ7" s="10" t="n"/>
+      <c r="AK7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>概要</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>指定した履歴行を取消する。対象行に `torikeshi_flg` を立て、値を前回値と入れ替えた打ち消し行（赤伝）を追加し、購読者マスタ（`t_dokusya`）を再計算する</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n"/>
+      <c r="AB8" s="10" t="n"/>
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="10" t="n"/>
+      <c r="AH8" s="10" t="n"/>
+      <c r="AI8" s="10" t="n"/>
+      <c r="AJ8" s="10" t="n"/>
+      <c r="AK8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>URI</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>/api/v1/dokusya/{dokusya_id}/rireki/{dokusya_rireki_id}/torikeshi</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n"/>
+      <c r="AB9" s="10" t="n"/>
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="10" t="n"/>
+      <c r="AH9" s="10" t="n"/>
+      <c r="AI9" s="10" t="n"/>
+      <c r="AJ9" s="10" t="n"/>
+      <c r="AK9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>メソッド</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="10" t="n"/>
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="10" t="n"/>
+      <c r="Z10" s="10" t="n"/>
+      <c r="AA10" s="10" t="n"/>
+      <c r="AB10" s="10" t="n"/>
+      <c r="AC10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n"/>
+      <c r="AG10" s="10" t="n"/>
+      <c r="AH10" s="10" t="n"/>
+      <c r="AI10" s="10" t="n"/>
+      <c r="AJ10" s="10" t="n"/>
+      <c r="AK10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>リクエストボディー</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>あり（`reason`）</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="10" t="n"/>
+      <c r="Z11" s="10" t="n"/>
+      <c r="AA11" s="10" t="n"/>
+      <c r="AB11" s="10" t="n"/>
+      <c r="AC11" s="10" t="n"/>
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AF11" s="10" t="n"/>
+      <c r="AG11" s="10" t="n"/>
+      <c r="AH11" s="10" t="n"/>
+      <c r="AI11" s="10" t="n"/>
+      <c r="AJ11" s="10" t="n"/>
+      <c r="AK11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>リクエストパラメーター</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>dokusya_id / dokusya_rireki_id（パスパラメータ）</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
+      <c r="Z12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n"/>
+      <c r="AB12" s="10" t="n"/>
+      <c r="AC12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n"/>
+      <c r="AG12" s="10" t="n"/>
+      <c r="AH12" s="10" t="n"/>
+      <c r="AI12" s="10" t="n"/>
+      <c r="AJ12" s="10" t="n"/>
+      <c r="AK12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>ヘッダ</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>HTTPレスポンスコード</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>取消しました</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="10" t="n"/>
+      <c r="AH14" s="10" t="n"/>
+      <c r="AI14" s="10" t="n"/>
+      <c r="AJ14" s="10" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="35" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>取消できないレコードです／入力値が不正です</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n"/>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="10" t="n"/>
+      <c r="Y15" s="10" t="n"/>
+      <c r="Z15" s="10" t="n"/>
+      <c r="AA15" s="10" t="n"/>
+      <c r="AB15" s="10" t="n"/>
+      <c r="AC15" s="10" t="n"/>
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="10" t="n"/>
+      <c r="AH15" s="10" t="n"/>
+      <c r="AI15" s="10" t="n"/>
+      <c r="AJ15" s="10" t="n"/>
+      <c r="AK15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="35" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="17" t="n">
+        <v>401</v>
+      </c>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>セッションが切れました</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n"/>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="10" t="n"/>
+      <c r="Z16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="10" t="n"/>
+      <c r="AC16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AF16" s="10" t="n"/>
+      <c r="AG16" s="10" t="n"/>
+      <c r="AH16" s="10" t="n"/>
+      <c r="AI16" s="10" t="n"/>
+      <c r="AJ16" s="10" t="n"/>
+      <c r="AK16" s="11" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="35" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="17" t="n">
+        <v>403</v>
+      </c>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <t>この画面へのアクセス権限がありません</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="10" t="n"/>
+      <c r="Z17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n"/>
+      <c r="AB17" s="10" t="n"/>
+      <c r="AC17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n"/>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="10" t="n"/>
+      <c r="AG17" s="10" t="n"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="10" t="n"/>
+      <c r="AJ17" s="10" t="n"/>
+      <c r="AK17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="35" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="17" t="n">
+        <v>404</v>
+      </c>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>指定された購読者／履歴が見つかりません</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="10" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="10" t="n"/>
+      <c r="AJ18" s="10" t="n"/>
+      <c r="AK18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="35" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="17" t="n">
+        <v>429</v>
+      </c>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="19" t="inlineStr">
+        <is>
+          <t>リクエスト回数が上限を超えました</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n"/>
+      <c r="AB19" s="10" t="n"/>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
+      <c r="AH19" s="10" t="n"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
+      <c r="AK19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="26" t="n"/>
+      <c r="J20" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>システムエラー</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="10" t="n"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="10" t="n"/>
+      <c r="Z20" s="10" t="n"/>
+      <c r="AA20" s="10" t="n"/>
+      <c r="AB20" s="10" t="n"/>
+      <c r="AC20" s="10" t="n"/>
+      <c r="AD20" s="10" t="n"/>
+      <c r="AE20" s="10" t="n"/>
+      <c r="AF20" s="10" t="n"/>
+      <c r="AG20" s="10" t="n"/>
+      <c r="AH20" s="10" t="n"/>
+      <c r="AI20" s="10" t="n"/>
+      <c r="AJ20" s="10" t="n"/>
+      <c r="AK20" s="11" t="n"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>2. リクエストパラメータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1"/>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>パラメーターID</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
+      </c>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
+      </c>
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG24" s="10" t="n"/>
+      <c r="AH24" s="10" t="n"/>
+      <c r="AI24" s="10" t="n"/>
+      <c r="AJ24" s="10" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>dokusya_id</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>対象購読者の dokusya_id（パスパラメータ）</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>dokusya_rireki_id</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="11" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="11" t="n"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="11" t="n"/>
+      <c r="Y26" s="17" t="inlineStr"/>
+      <c r="Z26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="17" t="inlineStr"/>
+      <c r="AD26" s="10" t="n"/>
+      <c r="AE26" s="11" t="n"/>
+      <c r="AF26" s="19" t="inlineStr">
+        <is>
+          <t>取消対象の履歴ID（パスパラメータ）。当該 dokusya_id に属する行であること</t>
+        </is>
+      </c>
+      <c r="AG26" s="10" t="n"/>
+      <c r="AH26" s="10" t="n"/>
+      <c r="AI26" s="10" t="n"/>
+      <c r="AJ26" s="10" t="n"/>
+      <c r="AK26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="B27" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="n"/>
+      <c r="O27" s="10" t="n"/>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="11" t="n"/>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="10" t="n"/>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="11" t="n"/>
+      <c r="Y27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="10" t="n"/>
+      <c r="AA27" s="10" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="11" t="n"/>
+      <c r="AF27" s="19" t="inlineStr">
+        <is>
+          <t>取消理由。対象行と打ち消し行の `biko` に書き込み、`t_log` の afterValue にも記録する（顧客要件）</t>
+        </is>
+      </c>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="10" t="n"/>
+      <c r="AI27" s="10" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
+      <c r="AK27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1"/>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1"/>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="10" t="n"/>
+      <c r="AC31" s="10" t="n"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>固定文言 `取消しました。`</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="108" customHeight="1">
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>POST /api/v1/dokusya/459/rireki/1024/torikeshi
+Content-Type: application/json
+{
+  "reason": "誤入力のため取消"
+}</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="10" t="n"/>
+      <c r="AF35" s="10" t="n"/>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "message": "取消しました。"
+}</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="10" t="n"/>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Torikeshi Not Allowed）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "TORIKESHI_NOT_ALLOWED",
+  "message": "取消できないレコードです（紙版・適用日が未来の末尾レコードのみ取消可能。新規・取消済・中間レコード・電子版・適用日到来済みは取消できません）。"
+}</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="10" t="n"/>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="10" t="n"/>
+      <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Validation Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "VALIDATION_ERROR",
+  "message": "入力値が不正です",
+  "errors": [{ "field": "reason", "message": "取消理由を入力してください。" }]
+}</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="10" t="n"/>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="72" customHeight="1">
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません。"
+}</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="n"/>
+      <c r="Y47" s="10" t="n"/>
+      <c r="Z47" s="10" t="n"/>
+      <c r="AA47" s="10" t="n"/>
+      <c r="AB47" s="10" t="n"/>
+      <c r="AC47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="10" t="n"/>
+      <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="11" t="n"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="B49" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 404 Not Found）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="72" customHeight="1">
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "NOT_FOUND",
+  "message": "指定された履歴が見つかりません。"
+}</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="10" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="10" t="n"/>
+      <c r="Z50" s="10" t="n"/>
+      <c r="AA50" s="10" t="n"/>
+      <c r="AB50" s="10" t="n"/>
+      <c r="AC50" s="10" t="n"/>
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AF50" s="10" t="n"/>
+      <c r="AG50" s="10" t="n"/>
+      <c r="AH50" s="10" t="n"/>
+      <c r="AI50" s="10" t="n"/>
+      <c r="AJ50" s="10" t="n"/>
+      <c r="AK50" s="11" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1"/>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>4. 処理手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>`dokusya_id` / `dokusya_rireki_id` を整数に変換する（`ParseIntPipe`）。変換できない場合 HTTP 400 `BAD_REQUEST`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>`reason` は必須・500文字以内（`TorikeshiRirekiDto`）。違反時 HTTP 400 `VALIDATION_ERROR`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>`SessionAuthGuard` → セッション不正なら HTTP 401 `UNAUTHORIZED`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="C59" s="41" t="inlineStr">
+        <is>
+          <t>`PermissionsGuard` で `dokusya.update` を検査 → 権限が無ければ HTTP 403 `FORBIDDEN`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="72" customHeight="1">
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>DataScope（購読者の所属JA／管理支店／所属支店。`fetchInScope` → `assertBranchScope` + `assertShitenScope`。所属支店はJA_KANRI_SHITENの一部アカウントのみ設定・顧客要件2026-07）を検査し、範囲外なら HTTP 404 でマスクする（行の存在を秘匿するため 403 ではなく 404）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>4.3 対象履歴の特定と取消可否判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="54" customHeight="1">
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>`dokusya_rireki_id` かつ `dokusya_id` の AND で 1 行取得する。当該購読者に属さない履歴IDを指定された場合は HTTP 404 `NOT_FOUND`（他購読者の履歴IDの探索を防ぐ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>`canTorikeshi` で可否を判定し、不可なら HTTP 400 `TORIKESHI_NOT_ALLOWED`。条件は画面設計書 §4.2 と同一：</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="54" customHeight="1">
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>判定はトランザクション開始前に行い、期待される検証失敗（400）をエラーログ（`log_type=3`）に残さない。境界競合に備え、トランザクション内の `applyTorikeshi` でも同じ判定を再実行する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>4.4 取消処理（トランザクション）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>4.5 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>`{ "message": "取消しました。" }` を HTTP 200 で返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>4.6 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>トランザクションが失敗した場合はロールバックし、エラーログ（`log_type=3`）をトランザクション外で記録したうえで例外を再送出する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等：HTTP 500 `INTERNAL_SERVER_ERROR`。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="116">
+    <mergeCell ref="J11:AK11"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="N18:AK18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="A53:AK53"/>
+    <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="C58:AK58"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="N19:AK19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="C44:AK44"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="B65:AK65"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="N20:AK20"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="B66:AK66"/>
+    <mergeCell ref="C38:AK38"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B61:AK61"/>
+    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="C35:AK35"/>
+    <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C55:AK55"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="J13:AK13"/>
+    <mergeCell ref="B14:I20"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="T32:X32"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="C62:AK62"/>
+    <mergeCell ref="B57:AK57"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="A29:AK29"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="C41:AK41"/>
+    <mergeCell ref="C50:AK50"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="V2:Y3"/>
+    <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="T27:X27"/>
+    <mergeCell ref="B54:AK54"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="A22:AK22"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B68:AK68"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="C31:L31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>